--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -2620,7 +2620,7 @@
       </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>Spec ready — REAL build (not already done): history table exists; add estimated-1RM trend chart + PR cards (heaviest/best e1RM/best volume) + token pass. epley1RM helper + per-session aggregation provided. HX1-Exercise-Detail-Spec.md</t>
+          <t>Built — pending merge/deploy. ExerciseHistory now leads with an Estimated-1RM trend MetricCard (Epley via shared epley1RM; sparkline + DeltaChip + interpretE1rmTrend gated to &gt;=2 sessions) + 3 per-session PR tiles (heaviest set / best e1RM / best volume); chronological table kept. Replaced the naive first-vs-last delta. tsc clean + 29 vitest pass (3 new interpretE1rmTrend cases). Weights kept kg (WK8 useWeightUnit = fast-follow). Visual confirm at post-deploy smoke.</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Spec ready — RE-SCOPED: client already sees adjustment history (expected/actual/deviation + new macros + coach notes). Gap = surface latest applied change as a plain-language banner moment (interpretAdjustment helper) + token pass. NU3-Nutrition-Checkin-Spec.md</t>
+          <t>Spec authored 2026-06-20 → docs/NU3-Nutrition-Checkin-Spec.md (in repo). RE-SCOPED: client already sees adjustment history; gap = surface latest APPLIED adjustment as a 'new target &amp; why' hero banner (interpretAdjustment helper, sign-trap-safe + MacroDistributionRibbon) + CC5 token pass. Implement on clean main AFTER CL2+HX1 merge (shares interpret.ts). Not yet built.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="J11" s="25" t="inlineStr">
         <is>
-          <t>Built — pending merge/deploy. PR-B: WeeklyProgressCard interpretation done. NutritionTargetsCard now CC1/CC2: per-macro % of calories + neutral-tone interpretMacroTargets() line (protein-forward/balanced/carb-led + goal intent), pure fn of stored grams (no BMR/TDEE). tsc clean + 26 vitest pass (incl new interpretMacroTargets cases). Visual confirm at post-deploy smoke.</t>
+          <t>Shipped — merged main PR #166 (ca6e822), deploys to prod via Vercel. WeeklyProgressCard (PR-B) + NutritionTargetsCard now CC1/CC2: per-macro % + interpretMacroTargets() line. Visual confirm at post-deploy smoke.</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>Built — pending merge/deploy. ExerciseHistory now leads with an Estimated-1RM trend MetricCard (Epley via shared epley1RM; sparkline + DeltaChip + interpretE1rmTrend gated to &gt;=2 sessions) + 3 per-session PR tiles (heaviest set / best e1RM / best volume); chronological table kept. Replaced the naive first-vs-last delta. tsc clean + 29 vitest pass (3 new interpretE1rmTrend cases). Weights kept kg (WK8 useWeightUnit = fast-follow). Visual confirm at post-deploy smoke.</t>
+          <t>Shipped — merged main PR #167 (1b5f9c6), deploys to prod via Vercel. ExerciseHistory leads with Estimated-1RM trend MetricCard (Epley via shared helper; sparkline+delta+interpretE1rmTrend gated &gt;=2 sessions) + 3 per-session PR tiles; chronological table kept. Visual confirm at post-deploy smoke.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Spec authored 2026-06-20 → docs/NU3-Nutrition-Checkin-Spec.md (in repo). RE-SCOPED: client already sees adjustment history; gap = surface latest APPLIED adjustment as a 'new target &amp; why' hero banner (interpretAdjustment helper, sign-trap-safe + MacroDistributionRibbon) + CC5 token pass. Implement on clean main AFTER CL2+HX1 merge (shares interpret.ts). Not yet built.</t>
+          <t>Shipped — merged main PR #168 (1fb91b0), deploys to prod via Vercel. ClientNutritionAdjustments now leads with a 'Your plan just updated' hero (latest applied adjustment: new kcal + MacroDistributionRibbon + interpretAdjustment 'new target &amp; why' line, sign-trap-safe) + CC5 token pass on history cards. tsc clean + 33 vitest. Visual confirm at post-deploy smoke.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G41" s="17" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>Shipped — merged main PR #168 (1fb91b0), deploys to prod via Vercel. ClientNutritionAdjustments now leads with a 'Your plan just updated' hero (latest applied adjustment: new kcal + MacroDistributionRibbon + interpretAdjustment 'new target &amp; why' line, sign-trap-safe) + CC5 token pass on history cards. tsc clean + 33 vitest. Visual confirm at post-deploy smoke.</t>
+          <t>RE-TARGET spec ready (v2) — docs/NU3-Nutrition-Checkin-Spec.md. #168 shipped the banner into orphaned ClientNutritionAdjustments.tsx (zero UI effect; caught in live smoke). v2: mount banner in NutritionProgress.tsx (team flow) wired to weekly_progress (calorie_adjustment/new_daily_calories), reuse interpretAdjustment helper (already in interpret.ts), CC5 token pass on per-week Alert, DELETE orphaned component. 1:1 flow out of scope (NutritionPhaseCard already a hero). Live-verify needs a seeded weekly_progress row (table empty pre-launch).</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J41" s="28" t="inlineStr">
         <is>
-          <t>RE-TARGET spec ready (v2) — docs/NU3-Nutrition-Checkin-Spec.md. #168 shipped the banner into orphaned ClientNutritionAdjustments.tsx (zero UI effect; caught in live smoke). v2: mount banner in NutritionProgress.tsx (team flow) wired to weekly_progress (calorie_adjustment/new_daily_calories), reuse interpretAdjustment helper (already in interpret.ts), CC5 token pass on per-week Alert, DELETE orphaned component. 1:1 flow out of scope (NutritionPhaseCard already a hero). Live-verify needs a seeded weekly_progress row (table empty pre-launch).</t>
+          <t>Shipped + LIVE-VERIFIED — re-targeted onto NutritionProgress.tsx (team flow), merged main PR #169 (1823ff2), on prod. Banner verified on theigu.com with a seeded weekly_progress row (since removed): green rail, 'Your plan just updated', 1,620 kcal hero + macro ribbon + interpretAdjustment line ('down 130 kcal... -0.8% vs -1% target'). Orphaned ClientNutritionAdjustments.tsx deleted. CC5 token pass applied. First attempt (#168) was dead-mount; caught by live smoke.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -4043,6 +4043,11 @@
           <t>Mobile landing best practice</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Shipped (code) — merged main PR #170 (4414be8), live on prod. Mobile sticky CTA bar (single-source primaryCta + IntersectionObserver, md:hidden, safe-area pb) + hero LCP &lt;link rel=preload as=image&gt;. tsc + build clean, faithful diff. LIVE MOBILE SMOKE NOT YET DONE: landing '/' is unreachable in waitlist mode (anon -&gt; /waitlist, logged-in -&gt; /dashboard) + Chrome resize didn't give a true &lt;=767px viewport. Self-verifies at launch (waitlist off); or add a mocked-logged_out component test for durable coverage.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="15" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -4283,6 +4283,11 @@
           <t>Standard pattern</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Shipped + LIVE-VERIFIED — merged main PR #171 (5da0522), on prod. og:image/twitter:image now ABSOLUTE https://theigu.com/og-image.png (was relative -&gt; broke scraper previews) + width/height/alt/locale; Organization enriched (square logo, areaServed Kuwait, contactPoint) + ProfessionalService Kuwait node (no prices, pending level-pricing). Verified live via served-HTML head fetch; both JSON-LD blocks schema-valid (0 err). OG image already on-brand (IGU wordmark, 2400x1260). NOTE: CMS social_links all empty -&gt; footer shows no socials + sameAs omitted (content to-do).</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="42" customHeight="1">
       <c r="A70" s="11" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5269,6 +5269,58 @@
       <c r="J88" s="24" t="inlineStr">
         <is>
           <t>Resolved — NOT a real bug. Stale cached dev bundle on the phone (long session: many HMR reloads + 2 LAN-IP changes + mirror reconnects) -&gt; module load failure -&gt; error boundary (same family as the SPA stale-chunk pattern). Disproven: CC faithful DB rebuild of the payment-exempt-sub shape + activity data rendered CLEAN in both Playwright Chromium AND real WebKit; and prod theigu.com/coach renders perfectly with the same real coach data. Dev-session artifact, not prod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WA1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Messaging</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Workout completion</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Add a "Message coach about this session" WhatsApp deep-link on the 1:1 workout completion sheet, pre-filled with the WK7 session recap (volume/sets/time/new PRs).</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Flagship of the hybrid messaging direction; WhatsApp is the preferred client&lt;-&gt;coach channel in-region; reuses existing WK7 summary + coach whatsapp_number.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>WorkoutCompletionSheet.tsx, WorkoutSessionV2.tsx, + get_coach_whatsapp_for_client RPC migration</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Ladder/Future coach contact</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Spec ready — docs/WA1-coach-whatsapp-session-button.md (2026-06-20). Needs new gated RPC (whatsapp not in get_coach_for_client) + sheet button + 1:1 service gate. Hybrid decision confirmed; in-app care-team messaging stays.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -5320,7 +5320,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Spec ready — docs/WA1-coach-whatsapp-session-button.md (2026-06-20). Needs new gated RPC (whatsapp not in get_coach_for_client) + sheet button + 1:1 service gate. Hybrid decision confirmed; in-app care-team messaging stays.</t>
+          <t>Shipped (code + RPC verified) — merged main PR #173 (b188445), live on prod. get_coach_whatsapp_for_client RPC registered (20260621120000 via migration repair+db push), SECURITY DEFINER, EXECUTE to authenticated/service_role only (anon denied). 'Message coach about this session' button on 1:1 workout-completion sheet (mobile+desktop), wa.me deep-link pre-filled from WK7 summary; team_plan excluded; separate ref-guarded fetch (not in loadSession burst). tsc+build clean. LIVE VISUAL smoke pending a 1:1 client + coach whatsapp_number set (team session won't show it by design). Bonus: 7 drifted WK8/WK9 migrations (20260619*) reconciled into schema_migrations.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -3949,6 +3949,11 @@
           <t>SaaS pricing pages (Mobbin Sites)</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Shipped + LIVE-VERIFIED -- merged main PR #174 (4f28d97), on prod. Services pricing clarity: 'Most popular' badge + ring/scale emphasis on the Hybrid card (slug-matched via service.slug=='hybrid', not name), tightened per-card CTAs (Join the team / Start online / Start hybrid / Start in-person via CTA_BY_SLUG), and the team start-date announcement block surfaced on Services (mirrors Index; loadTeamPlanSettings switched to .maybeSingle()). ComparisonTable untouched. Verified live on theigu.com/services after a hard-reload past a stale apex cache: Hybrid badge + emphasis, 4 tightened CTAs, prices 10/30/95/145, announcement renders ('Next team program starts soon!'; next_program_start_date null so the date sub-line is not exercised). tsc+build clean per CC. Note: PUB2 also pre-existed inside the Capacitor Phase-1 commit; de-duped during the feat/capacitor-mobile detangle (now main-only).</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="15" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -3902,6 +3902,11 @@
           <t>Future / WHOOP marketing sites (Mobbin Sites)</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Shipped (code) + deploy-verified -- merged main PR #175 (6d530c6), live on prod. Hero social-proof strip (new HeroSocialProof.tsx, sibling right after heroCtaRef so PUB4's IntersectionObserver bounds are untouched): founding-cohort pill (Star icon; FOUNDING_DEFAULT shown by default; CMS-overridable via homepage/social_proof.founding_line; hideable via founding_enabled='false') + a dormant 3-cell stats row where each cell renders only when its stat{n}_value is set; component returns null when nothing to show. No live DB read (pre-launch numbers are 1 coach/0 testimonials/0 paying -- numbers come only from CMS values). tsc+build clean, diff matches spec exactly. LIVE ANON SMOKE DEFERRED: landing '/' is unreachable while waitlist is ON (anon -&gt; /waitlist, logged-in -&gt; role home) -- confirmed via the main vercel.app alias redirecting anon to /waitlist. Self-verifies at launch (waitlist off); or preview now by toggling waitlist off in an incognito window. Content to-do (Hasan): founding line is live by default; populate homepage/social_proof stat rows in admin as real numbers/testimonials arrive (keys in docs/PUB1-Hero-Social-Proof-Spec.md).</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="11" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -4006,6 +4006,11 @@
           <t>Future / Centr coach bios</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Shipped (code) + deploy-verified -- merged main PR #176 (450a458), live on prod (production aliases theigu.com + www point to this deploy, state READY). MeetOurTeam coach cards now surface a 'Certifications' block (Award icon + first 2 qualifications as outline badges with truncate+title, plus '+N more') ABOVE specializations, gated on coach.qualifications presence -- certs that were dialog-only are now on the card. Lead styling / short_bio / specializations / CoachDetailDialog left untouched; free-text quals rendered directly (no getLabel). tsc+build clean; diff matches spec exactly. LIVE VISUAL SMOKE INCOMPLETE: /meet-our-team rendered but the Chrome automation could not snapshot it (page never reached document_idle -- open connections/hanging request in the admin session); this is a pure conditional render of already-fetched data, low risk -- re-eyeball via an authenticated session at leisure. Content (Hasan): lead coach has 9 quals populated (card shows MB BCh BAO (Hons) / ACE-CPT / +7 more), but short_bio (the philosophy/standout line) is empty -- populate a 1-2 sentence standout per coach.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="11" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -5023,7 +5023,7 @@
       </c>
       <c r="J83" s="24" t="inlineStr">
         <is>
-          <t>Reported - bugs cowork</t>
+          <t>Fixed (code-verified) -- merged main PR #177 (16bdf99), auto-deploys to prod via Vercel. Root cause: vaul ^0.9.9 defaults repositionInputs=true, so focusing the search field lifted the bottom sheet (the drift) and the keyboard-unaware max-h-[92dvh] pushed the 'Swap Exercise' title off-screen (the clip); the prior autoFocus-off only delayed it to the manual tap. Fix: SwapExercisePicker mobile Drawer (WorkoutSessionV2.tsx ~L1196) now passes repositionInputs={false} + shouldScaleBackground={false} -- the proven MobileDayDetail pattern -- so vaul stops translating the sheet and the title stays pinned above the keyboard. Coach SwapExerciseDialog (no input) + desktop overlay untouched; autoFocus kept off on mobile. tsc+build clean; diff matches spec. ON-DEVICE ACCEPTANCE TEST PENDING (NOT reproducible in desktop Chrome): iOS Safari + Android Chrome / Capacitor -- start session -&gt; Swap -&gt; tap Search -&gt; sheet stays put, title visible, filter+select work, desktop unchanged. Follow-up (separate, not BUG6): other input-bearing mobile Drawers (ExercisePickerDialog, CoachClientThread composer, MacrocycleEditor) may share the latent issue -- same one-line fix if reported.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1450,6 +1450,11 @@
           <t>Future / Oura home</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Shipped (code) -- merged main PR #178 (0f1b7b6), auto-deploys to prod via Vercel. Restructured the ACTIVE client dashboard overview in NewClientOverview.tsx (the live surface; the card-grid OverviewSection inside ClientDashboardLayout is orphaned dead code -- left untouched). New order: interrupts (PaymentAttentionBanner/AlertsCard) -&gt; one hero (TodaysWorkoutHero, with the programCount=0 'coach is preparing your program' empty-state preserved) -&gt; LogTodayCard -&gt; single-column ranked stack (NutritionTargets -&gt; WeeklyProgress -&gt; Adherence -&gt; Coach -&gt; CareTeam) -&gt; QuickActionsGrid -&gt; quiet 'Account' group (border-t + muted heading wrapping PlanBillingCard only). Both 2-col grids dropped; billing demoted; all 11 cards present exactly once with props/hooks/loadDashboardData/skeleton/empty-state unchanged (reorder only). tsc+build clean; diff matches spec. LIVE VISUAL SMOKE PENDING: /dashboard is auth-gated to an active client (admin/coach are redirected) so it is NOT reachable through the admin session -- verify the mobile single-column read, desktop-not-broken, and empty-state hero-swap via a test-client login or the Capacitor build. Client nutrition PAGE intentionally untouched (separate NU* items own it).</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="15" t="inlineStr">

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5341,6 +5341,58 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>Shipped (code + RPC verified) — merged main PR #173 (b188445), live on prod. get_coach_whatsapp_for_client RPC registered (20260621120000 via migration repair+db push), SECURITY DEFINER, EXECUTE to authenticated/service_role only (anon denied). 'Message coach about this session' button on 1:1 workout-completion sheet (mobile+desktop), wa.me deep-link pre-filled from WK7 summary; team_plan excluded; separate ref-guarded fetch (not in loadSession burst). tsc+build clean. LIVE VISUAL smoke pending a 1:1 client + coach whatsapp_number set (team session won't show it by design). Bonus: 7 drifted WK8/WK9 migrations (20260619*) reconciled into schema_migrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NU8</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nutrition (Team + 1:1)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Consolidate the client nutrition pages into one scroll: remove the Goal Setting/Progress Tracker top tabs AND the nested Progress/Graphs tabs; targets hero with an Edit-targets sheet, inline trend (range + Weight/Body-fat toggle), weekly check-ins. Unify team + 1:1.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Removes 3-layer redundant tab nesting; information scent; Mobbin-grounded.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TeamNutrition.tsx, NutritionProgress.tsx, NutritionGoal.tsx, ClientNutrition.tsx</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>MacroFactor / Lifesum / Yazio / Alma / MyFitnessPal (ios)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Phase 1 (team) SHIPPED + LIVE (deploy-verified) -- merged main PR #179 (7f8e92b); production aliases (theigu.com/www) point to it, READY. TeamNutrition consolidated to one scroll: top-level Goal/Progress tabs + nested Progress/Graphs tabs removed. Hero gained MacroDistributionRibbon + an 'Edit targets' responsive sheet (mobile vaul Drawer repositionInputs=false per BUG6 + DrawerScrollArea; desktop Dialog + DialogScrollArea) hosting NutritionGoal(onSaved=close+refresh) -- replaces the navigate-away 'Change Goal'. Inline trend = 4W/12W/All range pills + Weight|Body-fat toggle (weeklyProgress filtered upstream; graph internals untouched); WeekCard list unchanged; no-goal empty state opens the sheet. NutritionGoal gained optional onSaved prop (non-breaking). tsc+build+eslint clean; diff matches spec. TEST-CLIENT VISUAL PENDING (auth-gated to active team client; admin/coach redirected) -- verify sheet save-&gt;close-&gt;refresh, trend range/toggle, and mobile keyboard via a team test-client login / Capacitor. FOLLOW-UPS (minor, non-blocking): (1) stray ?tab= links in QuickActionsGrid/AlertsCard now no-op -- tidy; (2) loadData's 'No Active Goal' destructive toast fires on the first-time no-goal path next to the 'Set your targets' empty state -- misleading, soften/remove. PHASE 2 (1:1 ClientNutrition alignment) PENDING -- separate branch/PR per docs/NU-Client-Nutrition-Redesign-Spec.md.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Shipped (code) -- merged main PR #178 (0f1b7b6), auto-deploys to prod via Vercel. Restructured the ACTIVE client dashboard overview in NewClientOverview.tsx (the live surface; the card-grid OverviewSection inside ClientDashboardLayout is orphaned dead code -- left untouched). New order: interrupts (PaymentAttentionBanner/AlertsCard) -&gt; one hero (TodaysWorkoutHero, with the programCount=0 'coach is preparing your program' empty-state preserved) -&gt; LogTodayCard -&gt; single-column ranked stack (NutritionTargets -&gt; WeeklyProgress -&gt; Adherence -&gt; Coach -&gt; CareTeam) -&gt; QuickActionsGrid -&gt; quiet 'Account' group (border-t + muted heading wrapping PlanBillingCard only). Both 2-col grids dropped; billing demoted; all 11 cards present exactly once with props/hooks/loadDashboardData/skeleton/empty-state unchanged (reorder only). tsc+build clean; diff matches spec. LIVE VISUAL SMOKE PENDING: /dashboard is auth-gated to an active client (admin/coach are redirected) so it is NOT reachable through the admin session -- verify the mobile single-column read, desktop-not-broken, and empty-state hero-swap via a test-client login or the Capacitor build. Client nutrition PAGE intentionally untouched (separate NU* items own it).</t>
+          <t>Shipped + LIVE-VERIFIED (2026-06-23) -- merged main PR #178 (0f1b7b6), live on prod. Restructured the ACTIVE client dashboard overview in NewClientOverview.tsx (the card-grid OverviewSection in ClientDashboardLayout is orphaned dead code, untouched). Verified live via a team client (Hasan, desktop, /dashboard): interrupts (AlertsCard 'Missing Weight Logs') -&gt; Today's Workout hero -&gt; single-column ranked stack (Daily Targets -&gt; This Week -&gt; Adherence -&gt; Your Coach -&gt; My Care Team) -&gt; QuickActionsGrid (Weekly Check-In / Nutrition / Exercise Library) -&gt; quiet 'Account' group (border-t + muted heading) with PlanBillingCard demoted to the bottom. Both 2-col grids gone; all cards present once. tsc+build clean. Mobile reads the same single column (grids dropped); explicit phone pass optional.</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Shipped (code) + deploy-verified -- merged main PR #176 (450a458), live on prod (production aliases theigu.com + www point to this deploy, state READY). MeetOurTeam coach cards now surface a 'Certifications' block (Award icon + first 2 qualifications as outline badges with truncate+title, plus '+N more') ABOVE specializations, gated on coach.qualifications presence -- certs that were dialog-only are now on the card. Lead styling / short_bio / specializations / CoachDetailDialog left untouched; free-text quals rendered directly (no getLabel). tsc+build clean; diff matches spec exactly. LIVE VISUAL SMOKE INCOMPLETE: /meet-our-team rendered but the Chrome automation could not snapshot it (page never reached document_idle -- open connections/hanging request in the admin session); this is a pure conditional render of already-fetched data, low risk -- re-eyeball via an authenticated session at leisure. Content (Hasan): lead coach has 9 quals populated (card shows MB BCh BAO (Hons) / ACE-CPT / +7 more), but short_bio (the philosophy/standout line) is empty -- populate a 1-2 sentence standout per coach.</t>
+          <t>Shipped + LIVE-VERIFIED (2026-06-23) -- merged main PR #176 (450a458), live on prod. MeetOurTeam coach cards now surface a 'Certifications' block (Award icon + first 2 qualifications as outline badges + '+N more') ABOVE Specializations, gated on coach.qualifications. Verified live on theigu.com/meet-our-team (authenticated client session): lead coach (Hasan Dashti, Lead badge + red ring) shows Certifications = 'MB BCh BAO (Hons)' / 'ACE-CPT' / '+7 more', then Specializations (General Fitness/Strength Training/Bodybuilding/+6 more). Lead styling / CoachDetailDialog / specializations untouched; free-text quals rendered directly (no getLabel). tsc+build clean; diff matches spec. CONTENT (Hasan): lead coach short_bio (the philosophy/standout line) is still empty -- card shows no standout line; populate a 1-2 sentence standout per coach.</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Phase 1 (team) SHIPPED + LIVE (deploy-verified) -- merged main PR #179 (7f8e92b); production aliases (theigu.com/www) point to it, READY. TeamNutrition consolidated to one scroll: top-level Goal/Progress tabs + nested Progress/Graphs tabs removed. Hero gained MacroDistributionRibbon + an 'Edit targets' responsive sheet (mobile vaul Drawer repositionInputs=false per BUG6 + DrawerScrollArea; desktop Dialog + DialogScrollArea) hosting NutritionGoal(onSaved=close+refresh) -- replaces the navigate-away 'Change Goal'. Inline trend = 4W/12W/All range pills + Weight|Body-fat toggle (weeklyProgress filtered upstream; graph internals untouched); WeekCard list unchanged; no-goal empty state opens the sheet. NutritionGoal gained optional onSaved prop (non-breaking). tsc+build+eslint clean; diff matches spec. TEST-CLIENT VISUAL PENDING (auth-gated to active team client; admin/coach redirected) -- verify sheet save-&gt;close-&gt;refresh, trend range/toggle, and mobile keyboard via a team test-client login / Capacitor. FOLLOW-UPS (minor, non-blocking): (1) stray ?tab= links in QuickActionsGrid/AlertsCard now no-op -- tidy; (2) loadData's 'No Active Goal' destructive toast fires on the first-time no-goal path next to the 'Set your targets' empty state -- misleading, soften/remove. PHASE 2 (1:1 ClientNutrition alignment) PENDING -- separate branch/PR per docs/NU-Client-Nutrition-Redesign-Spec.md.</t>
+          <t>Phase 1 (team) SHIPPED + LIVE-VERIFIED (2026-06-23) -- merged main PR #179 (7f8e92b), live on prod. Verified live via a team client (Hasan, desktop, /nutrition-team): one scroll, NO tabs (Goal/Progress + nested Progress/Graphs both removed), new subtitle. Hero = Fat Loss Phase, Current Targets 1751 kcal + MacroDistributionRibbon (P138/F78/C124, red/amber/blue) + 'Edit targets'. Edit targets opens the responsive sheet (desktop Dialog) hosting the NutritionGoal editor (donut + targets + journey + its own Change Goal) in-context with no navigation, closes cleanly. Trend block: 4W/12W/All range pills + Weight|Body-fat toggle (toggle swaps the graph live); Weekly Logs WeekCard expanded with the full check-in form. NutritionGoal gained optional onSaved. tsc+build+eslint clean. REMAINING: mobile Drawer + keyboard (repositionInputs=false) still needs a phone/Capacitor pass; the save-&gt;deactivate+insert goal cycle was NOT triggered live (would mutate the test client's goal). FOLLOW-UPS (minor): (1) stray ?tab= links in QuickActionsGrid/AlertsCard now no-op -- tidy; (2) loadData 'No Active Goal' destructive toast on the first-time no-goal path -- soften. PHASE 2 (1:1 ClientNutrition alignment) PENDING -- separate branch/PR per docs/NU-Client-Nutrition-Redesign-Spec.md.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -5392,7 +5392,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Phase 1 (team) SHIPPED + LIVE-VERIFIED (2026-06-23) -- merged main PR #179 (7f8e92b), live on prod. Verified live via a team client (Hasan, desktop, /nutrition-team): one scroll, NO tabs (Goal/Progress + nested Progress/Graphs both removed), new subtitle. Hero = Fat Loss Phase, Current Targets 1751 kcal + MacroDistributionRibbon (P138/F78/C124, red/amber/blue) + 'Edit targets'. Edit targets opens the responsive sheet (desktop Dialog) hosting the NutritionGoal editor (donut + targets + journey + its own Change Goal) in-context with no navigation, closes cleanly. Trend block: 4W/12W/All range pills + Weight|Body-fat toggle (toggle swaps the graph live); Weekly Logs WeekCard expanded with the full check-in form. NutritionGoal gained optional onSaved. tsc+build+eslint clean. REMAINING: mobile Drawer + keyboard (repositionInputs=false) still needs a phone/Capacitor pass; the save-&gt;deactivate+insert goal cycle was NOT triggered live (would mutate the test client's goal). FOLLOW-UPS (minor): (1) stray ?tab= links in QuickActionsGrid/AlertsCard now no-op -- tidy; (2) loadData 'No Active Goal' destructive toast on the first-time no-goal path -- soften. PHASE 2 (1:1 ClientNutrition alignment) PENDING -- separate branch/PR per docs/NU-Client-Nutrition-Redesign-Spec.md.</t>
+          <t>BOTH PHASES SHIPPED + LIVE-VERIFIED (2026-06-23). Client nutrition consolidated to one scroll, zero tabs, team + 1:1 sharing the shape (hero -&gt; log -&gt; trend -&gt; weekly input). PHASE 1 (team, PR #179 7f8e92b): /nutrition-team verified live via a team client -- no tabs, hero + macro ribbon + 'Edit targets' Dialog hosting the goal editor in-context, 4W/12W/All range + Weight|Body-fat toggle, WeekCard check-ins. PHASE 2 (1:1, PR #180 69c9729): /nutrition-client verified live via a seeded 1:1-Online test client -- NutritionPhaseCard hero (read-only, 'On Track', 2100 kcal + ribbon, expected vs actual rate strip computed from seeded weight logs) + 'Message coach to adjust' link + weekly ribbon + inline Log Today + trend (range/toggle on real seeded data, weight line vs target) + 'This week' ClientNutritionProgress form. No tabs. NutritionGoal gained optional onSaved. tsc+build+eslint clean on both. TEST ACCOUNTS (payment-exempt, +alias emails): Team / 1:1 Online / 1:1 Hybrid / 1:1 In-Person created by Hasan; 3 1:1 accounts seeded with active nutrition_phases (Summer Cut / Lean Bulk / Fat Loss Phase) + 9 weight_logs on Online -- retained for ongoing feature testing. REMAINING: mobile Drawer + keyboard (NU Phase 1 Edit-targets sheet, repositionInputs=false) still needs a phone/Capacitor pass. FOLLOW-UPS (minor): stray ?tab= links in QuickActionsGrid/AlertsCard now no-op; loadData 'No Active Goal' destructive toast on first-time no-goal path -- soften.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -2143,6 +2143,11 @@
           <t>Superhuman / Front list rows</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Phase 1 SHIPPED + LIVE-VERIFIED (2026-06-23) -- merged main PR #181 (a604aea), live on prod. Coach My Clients roster redesigned (CoachMyClientsPage.tsx): needs-attention strip on top (jump chips from get_coach_roster_attention tiles/client_ids + awaitingPayment count; zero-count muted) + ACTIVE-FIRST reorder (action sections moved below, collapse-when-empty) + scannable two-line row (rail · name · plan / status · adherence · check-ins · last weigh-in, sm:grid-cols-4 aligned columns) + consolidated alert cluster (check-in-overdue / payment / adjustment from client_ids + unread + deload; icons only when flagged). Verified live via coach test session (4 wired test clients): strip shows '1 check-ins overdue · 9d' (seeded +hybrid quiet client) and that row shows the Clock alert icon; active roster leads; aligned columns render. tsc+build+eslint clean. PHASE 1 LIMITATION (RLS, confirmed live): the row's 'Last weigh-in' reads weight_logs CLIENT-SIDE, which coach RLS hides, so it shows 'No check-in' for ALL rows (even +online which has 9 logs). The strip's overdue count is correct because it comes from the SECURITY DEFINER RPC. =&gt; PHASE 2 RPC must feed last-weigh-in + adherence + check-ins X/3 (not just adherence). PHASE 2 PENDING: get_coach_roster_stats() / useCoachRosterStats() for adherence % + weekly check-ins + no-program alert + adherence sort -- own branch/PR per docs/RO-Coach-Roster-Redesign-Spec.md.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -2188,6 +2193,11 @@
       <c r="I25" s="16" t="inlineStr">
         <is>
           <t>CRM inboxes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SHIPPED (RO Phase 1, PR #181 a604aea, live + verified 2026-06-23) -- added 'Check-in due' sort (days_since_check_in desc, nulls last) alongside At-risk-first + Name, beside the existing search + plan filter. Adherence sort deferred to RO Phase 2 (needs the stats RPC).</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1950,6 +1950,11 @@
           <t>Intercom Inbox</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Shipped + LIVE-VERIFIED (2026-06-23) -- merged main PR #183 (57e7720), live on prod. Coach client view is now a MASTER-DETAIL workspace inside the coach shell (new CoachClientsWorkspace): the CoachSidebar global nav is preserved (no more dead-end page), a persistent compact roster on the left (reuses the roster hooks -- name + plan + adherence/check-ins + alert dots + urgency rail, search + sort, 'Full queue' -&gt; ?view=queue keeps Pending/At-Risk/approvals reachable), and the selected client's detail (ClientOverviewPanel, extracted from the now-deleted standalone CoachClientOverview) in the right pane. App.tsx repoints /coach/clients/:id into CoachDashboard (shell); CoachDashboard derives section from the path. Verified live via coach session (desktop): clicking a client swaps the RIGHT PANE CLIENT-SIDE (no reload), master stays, row highlights, sidebar persists, the 8 section tabs work; 'Select a client' empty state when none selected; check-ins X/3 + tone + alert dots populate from the RO Phase 2 RPC. tsc+build+eslint clean. KNOWN FOLLOW-UP (separate ticket): the detail's Overview 'Last weigh-in' card + Nutrition trend still read weight_logs client-side (coach RLS) -&gt; 'No weigh-ins yet' even with logs; needs a coach-scoped read like get_coach_roster_stats. MOBILE pending a phone pass (drawer master + the two 'Clients' buttons + lg pane-height calc(100vh-12rem) nudge). Pairs with CO7 (per-tab accordion) if desired -- separate.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -2145,7 +2150,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Phase 1 SHIPPED + LIVE-VERIFIED (2026-06-23) -- merged main PR #181 (a604aea), live on prod. Coach My Clients roster redesigned (CoachMyClientsPage.tsx): needs-attention strip on top (jump chips from get_coach_roster_attention tiles/client_ids + awaitingPayment count; zero-count muted) + ACTIVE-FIRST reorder (action sections moved below, collapse-when-empty) + scannable two-line row (rail · name · plan / status · adherence · check-ins · last weigh-in, sm:grid-cols-4 aligned columns) + consolidated alert cluster (check-in-overdue / payment / adjustment from client_ids + unread + deload; icons only when flagged). Verified live via coach test session (4 wired test clients): strip shows '1 check-ins overdue · 9d' (seeded +hybrid quiet client) and that row shows the Clock alert icon; active roster leads; aligned columns render. tsc+build+eslint clean. PHASE 1 LIMITATION (RLS, confirmed live): the row's 'Last weigh-in' reads weight_logs CLIENT-SIDE, which coach RLS hides, so it shows 'No check-in' for ALL rows (even +online which has 9 logs). The strip's overdue count is correct because it comes from the SECURITY DEFINER RPC. =&gt; PHASE 2 RPC must feed last-weigh-in + adherence + check-ins X/3 (not just adherence). PHASE 2 PENDING: get_coach_roster_stats() / useCoachRosterStats() for adherence % + weekly check-ins + no-program alert + adherence sort -- own branch/PR per docs/RO-Coach-Roster-Redesign-Spec.md.</t>
+          <t>Phase 1 SHIPPED + LIVE-VERIFIED (2026-06-23) -- merged main PR #181 (a604aea), live on prod. Coach My Clients roster redesigned (CoachMyClientsPage.tsx): needs-attention strip on top (jump chips from get_coach_roster_attention tiles/client_ids + awaitingPayment count; zero-count muted) + ACTIVE-FIRST reorder (action sections moved below, collapse-when-empty) + scannable two-line row (rail · name · plan / status · adherence · check-ins · last weigh-in, sm:grid-cols-4 aligned columns) + consolidated alert cluster (check-in-overdue / payment / adjustment from client_ids + unread + deload; icons only when flagged). Verified live via coach test session (4 wired test clients): strip shows '1 check-ins overdue · 9d' (seeded +hybrid quiet client) and that row shows the Clock alert icon; active roster leads; aligned columns render. tsc+build+eslint clean. PHASE 1 LIMITATION (RLS, confirmed live): the row's 'Last weigh-in' reads weight_logs CLIENT-SIDE, which coach RLS hides, so it shows 'No check-in' for ALL rows (even +online which has 9 logs). The strip's overdue count is correct because it comes from the SECURITY DEFINER RPC. =&gt; PHASE 2 RPC must feed last-weigh-in + adherence + check-ins X/3 (not just adherence). PHASE 2 PENDING: get_coach_roster_stats() / useCoachRosterStats() for adherence % + weekly check-ins + no-program alert + adherence sort -- own branch/PR per docs/RO-Coach-Roster-Redesign-Spec.md. || PHASE 2 LIVE-VERIFIED (2026-06-23): get_coach_roster_stats() applied to prod (RO Phase 2 PR #182 frontend merged; function applied via MCP raw SQL -- SECURITY DEFINER, anon revoked, authenticated granted; a later supabase db push registers the merged migration cleanly). Roster + the CO6 master now show real check-ins X/3 + RPC-fed last-weigh-in (fixes the Phase-1 RLS 'No check-in') + no-program/alert dots; adherence shows '--' until adherence_logs/weekly_progress adherence data exists for these clients. Confirmed live in the coach session.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2202,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SHIPPED (RO Phase 1, PR #181 a604aea, live + verified 2026-06-23) -- added 'Check-in due' sort (days_since_check_in desc, nulls last) alongside At-risk-first + Name, beside the existing search + plan filter. Adherence sort deferred to RO Phase 2 (needs the stats RPC).</t>
+          <t>SHIPPED (RO Phase 1, PR #181 a604aea, live + verified 2026-06-23) -- added 'Check-in due' sort (days_since_check_in desc, nulls last) alongside At-risk-first + Name, beside the existing search + plan filter. Adherence sort deferred to RO Phase 2 (needs the stats RPC). Adherence sort now ACTIVE (RO Phase 2 live).</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5408,6 +5408,162 @@
       <c r="J90" t="inlineStr">
         <is>
           <t>BOTH PHASES SHIPPED + LIVE-VERIFIED (2026-06-23). Client nutrition consolidated to one scroll, zero tabs, team + 1:1 sharing the shape (hero -&gt; log -&gt; trend -&gt; weekly input). PHASE 1 (team, PR #179 7f8e92b): /nutrition-team verified live via a team client -- no tabs, hero + macro ribbon + 'Edit targets' Dialog hosting the goal editor in-context, 4W/12W/All range + Weight|Body-fat toggle, WeekCard check-ins. PHASE 2 (1:1, PR #180 69c9729): /nutrition-client verified live via a seeded 1:1-Online test client -- NutritionPhaseCard hero (read-only, 'On Track', 2100 kcal + ribbon, expected vs actual rate strip computed from seeded weight logs) + 'Message coach to adjust' link + weekly ribbon + inline Log Today + trend (range/toggle on real seeded data, weight line vs target) + 'This week' ClientNutritionProgress form. No tabs. NutritionGoal gained optional onSaved. tsc+build+eslint clean on both. TEST ACCOUNTS (payment-exempt, +alias emails): Team / 1:1 Online / 1:1 Hybrid / 1:1 In-Person created by Hasan; 3 1:1 accounts seeded with active nutrition_phases (Summer Cut / Lean Bulk / Fat Loss Phase) + 9 weight_logs on Online -- retained for ongoing feature testing. REMAINING: mobile Drawer + keyboard (NU Phase 1 Edit-targets sheet, repositionInputs=false) still needs a phone/Capacitor pass. FOLLOW-UPS (minor): stray ?tab= links in QuickActionsGrid/AlertsCard now no-op; loadData 'No Active Goal' destructive toast on first-time no-goal path -- soften.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>SE1</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Coach SessionsTab + client /sessions</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Redesign to grouped Upcoming/Past lists (date chips + status pills) both sides; then request-&gt;confirm booking (client requests status=requested -&gt; coach confirms/declines); availability slots later phase</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Sessions surface is a bare ad-hoc digest; both coach+client need to book; clean Sessions(appointments) vs Workouts(training) boundary</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>client-overview/tabs/SessionsTab.tsx, pages/sessions, direct_calendar_sessions</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>Calendly / Cal.com booking; Practo appointments</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Spec ready - docs/SE-Sessions-Tab-Booking-Spec.md (CC handoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>WK10</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Workout</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Coach client Workouts tab</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Calendar-forward week grid + per-day +menu (Blank / Saved / Assign program in-context / Create program scoped to client) + Program history strip; reuse DirectClientCalendar/AssignFromLibraryDialog/ClientProgramList</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Today Assign navigates away + calendar hidden in a Sheet; no at-a-glance week; building custom program abandons the client page</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>client-overview/tabs/WorkoutsTab.tsx, coach/programs/*</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
+        <is>
+          <t>TrueCoach calendar; Runna day-list</t>
+        </is>
+      </c>
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>Spec ready - docs/WK-Coach-Workouts-Calendar-Spec.md (CC handoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>GC1</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Coach + client</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Google Calendar 2-way sync of booked sessions (OAuth + Calendar API + token storage/refresh; reminders; later read busy-times). Must work inside Capacitor WebView for native.</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Sessions land in the personal calendars both sides actually live in; reduces no-shows</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>new edge fns + token table; direct_calendar_sessions</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>Calendly GCal connect</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>Future phase - after Sessions booking (Phase 2) ships. Captured; not started</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5564,6 +5564,162 @@
       <c r="J93" s="24" t="inlineStr">
         <is>
           <t>Future phase - after Sessions booking (Phase 2) ships. Captured; not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>PR1</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Coach client Progress tab</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Add CC1 metric-card summary row (weight/body-fat/volume + deltas + sparklines) + status header above the existing weight-trend hero; two-up Measurements + Volume below. Display-only regroup of CoachNutritionGraphs + VolumeChart</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Raw chart dump today; the numbers a coach scans first arent surfaced; no shared visual language</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>client-overview/tabs/ProgressTab.tsx, CoachNutritionGraphs, VolumeChart</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>Oura/WHOOP insights; CC1 metric card</t>
+        </is>
+      </c>
+      <c r="J94" s="24" t="inlineStr">
+        <is>
+          <t>Spec + mock ready - docs/PR-Progress-Tab-Redesign-Spec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>CT1</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Care Team</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>CareTeamCard + CareTeamMessagesPanel</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Polish roster to role-coloured chips (coach/dietitian/physio) + staff-only banner; restyle team thread to own-vs-other bubbles w/ mentions. Presentation pass, no schema/RLS change</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Components predate the current card/chip/thread language; read as a flat list + log</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>coach/CareTeamCard.tsx, nutrition/CareTeamMessagesPanel.tsx</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>Slack threads; clinical care-team UIs</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>Spec + mock ready - docs/CT-CareTeam-Tab-Redesign-Spec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>PF1</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Coach client Profile tab</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Add identity header card (avatar+name+plan+status pill); swap shadcn Badges for the standard rounded status pills; auto-fit the demographics grid. Light polish, already well-built, read-only kept</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Tab leads straight into a stat grid with no face; badge style inconsistent with the rest of the redesign</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>client-overview/tabs/ProfileInfoTab.tsx</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>CRM contact records</t>
+        </is>
+      </c>
+      <c r="J96" s="24" t="inlineStr">
+        <is>
+          <t>Spec + mock ready - docs/PF-Profile-Tab-Redesign-Spec.md</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5720,6 +5720,162 @@
       <c r="J96" s="24" t="inlineStr">
         <is>
           <t>Spec + mock ready - docs/PF-Profile-Tab-Redesign-Spec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>CL2</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Client dashboard (NewClientOverview)</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Visual polish to coach-grade language: drop gradient bg for flat surface; add CC1 glance-card row; emerald rail on Todays Workout hero; MacroDistributionRibbon on nutrition target card; rounded status pills; demoted Account group. IA from CL1 unchanged</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard still uses gradient bg + generic border cards; reads as a different product from coach surfaces + the shipped Nutrition tab</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>client/ClientDashboardLayout.tsx, client/NewClientOverview.tsx + composed cards</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>Coach Overview/Nutrition (own); Runna/Caliber home</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="inlineStr">
+        <is>
+          <t>Spec + mock ready - docs/CL2-Client-Dashboard-Polish-Spec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>NU9</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Client nutrition This-week form (ClientNutritionProgress)</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Restructure the weekly tracking form into a completion-state card stack (weigh-ins/steps/bodyfat+circumference/weekly check-in) w/ status rails + chips matching ClientWeeklyRibbon; mobile Drawer for the heavy inputs. Keep all writes incl bodyfat dual-write</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Only laggard on /nutrition-client: still generic shadcn cards, no completion signalling; heaviest client interaction</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>nutrition/ClientNutritionProgress.tsx</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>Coach Nutrition (own); habit trackers</t>
+        </is>
+      </c>
+      <c r="J98" s="24" t="inlineStr">
+        <is>
+          <t>Spec + mock ready - docs/NU9-Client-ThisWeek-Tracking-Redesign-Spec.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>CO9</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>My Clients master-detail grid</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Collapse the master COLUMN width (340px to 220px) when a client is open, not just the card content -- the point of collapsing is to hand the freed width to the detail pane. Smooth grid-template-columns transition</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Polish batch condensed the card content but kept the 340px column, so the detail pane gained no room (Hasan caught live)</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>coach/CoachClientsWorkspace.tsx:351</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>TrueCoach/Linear master-detail</t>
+        </is>
+      </c>
+      <c r="J99" s="24" t="inlineStr">
+        <is>
+          <t>Shipped (commit ad62f40); pending Vercel deploy + post-deploy smoke</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -5726,7 +5726,7 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>CL2</t>
+          <t>CL3</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="J97" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/CL2-Client-Dashboard-Polish-Spec.md</t>
+          <t>Increment 1 SHIPPED (commit a9b7fa6): flat surfaces (drop gradients) + macro ribbon on daily targets. Remaining: optional glance row + status-pill pass. Spec docs/CL2-Client-Dashboard-Polish-Spec.md</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5876,6 +5876,58 @@
       <c r="J99" s="24" t="inlineStr">
         <is>
           <t>Shipped (commit ad62f40); pending Vercel deploy + post-deploy smoke</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>BUG10</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>Coach client detail: Progress/Overview/Nutrition</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Coach saw "No measurements available" despite client weigh-ins existing. Root cause: weight_logs/circumference_logs coach SELECT keyed on nutrition_phases.coach_id (NULL on seeded phase + stale after reassignment). Fix: relationship-based policy via is_care_team_member_for_client, mirroring body_fat_logs</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Coach progress surfaces were empty even with logged data -- silently useless for any client whose phase.coach_id is NULL/stale</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>migration 20260624140000; weight_logs + circumference_logs RLS</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J100" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-24 (applied out-of-band; coach now sees 9 weigh-ins, -1.0kg, chart). Migration file pending commit + db push register</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -5823,7 +5823,7 @@
       </c>
       <c r="J98" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/NU9-Client-ThisWeek-Tracking-Redesign-Spec.md</t>
+          <t>Increment 1 SHIPPED + LIVE-VERIFIED 2026-06-25 (974b17d): This-week completion anchor (rail + chips) + removed dead Add Inputs button. Optional follow-up: section-card rails. NOTE pre-existing phase-week vs calendar-week count mismatch (anchor 0/3 vs ribbon 1/3)</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5928,6 +5928,58 @@
       <c r="J100" s="24" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-06-24 (applied out-of-band; coach now sees 9 weigh-ins, -1.0kg, chart). Migration file pending commit + db push register</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>BUG11</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Bug fix</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Client nutrition (/nutrition-client)</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Weigh-in count disagreed on the same page: top ribbon showed 1/3 (IGU calendar week) while the new This-week anchor + check-in save-gate showed 0/3 (phase-week). Aligned ClientNutritionProgress anchor + save-gate + N-more notice to startOfIguWeek, matching ribbon + dashboard</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>User sees two different weigh-in counts seconds apart; save button gated on a different number than displayed</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>nutrition/ClientNutritionProgress.tsx</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J101" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (459befe): anchor now reads 1/3 in agreement with the ribbon</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5980,6 +5980,266 @@
       <c r="J101" s="24" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (459befe): anchor now reads 1/3 in agreement with the ribbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>CL6</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Client dashboard (NewClientOverview)</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Desktop: pair right-sized cards 2-col (Daily Targets + Log Today, Weekly Progress + Adherence, Coach + Care Team) instead of full-width stacking. Banners/hero stay full width; mobile stays stacked</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Cards stacked full-width even when small (e.g. Log Today = 2 inputs) -- wasted space, poor scan on desktop</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>client/NewClientOverview.tsx</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J102" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (fc77900): Targets+Log side by side confirmed live</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>CL7</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Standalone client pages (nutrition, calendar, team-nutrition)</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>New ClientPageLayout shell (SidebarProvider + ClientSidebar + flat bg). Wrapped ClientNutrition + TeamNutrition so the left nav persists + gradient dropped. WorkoutCalendar gets it via WK10</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Sub-pages rendered bare -- left sidebar disappeared + still had the old gradient bg (inconsistent w/ flat dashboard). Hasan flagged it repeated across sub-pages</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>components/layouts/ClientPageLayout.tsx (new); pages/ClientNutrition.tsx; pages/TeamNutrition.tsx</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J103" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (9937518): nutrition page now has left sidebar + flat bg</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>CL8</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard Your Coach card (CoachCard)</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Surface the WhatsApp contact-coach button on the dashboard (was only wired into the post-workout completion sheet). Green Message on WhatsApp button w/ the real WhatsApp glyph, gated on coach having a number, via get_coach_whatsapp_for_client RPC; stopPropagation so it does not trigger the cards profile-nav</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>Built WhatsApp contact feature was invisible to clients on the dashboard; Hasan asked where it was + wanted the real WA logo</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>client/CoachCard.tsx</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J104" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (550c964): green WhatsApp button renders on Your Coach card</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>CL9</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>Client nutrition page (/nutrition-client)</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Regroup desktop layout: Row A = target/calorie phase card beside the trend graph; Row B = weekly ribbon + daily log paired; This-week form full width. lg breakpoint (sidebar eats width on md)</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Cards stacked full-width single column -- oversized for content, related info (target + graph) not grouped. Hasan flagged grouping + sizing</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>pages/ClientNutrition.tsx</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J105" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (3fcf6dd): phase card beside graph, not cramped; ribbon+log paired</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>WK11</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Workout</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Client workout calendar (/client/workout/calendar)</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Rebuilt the bare month-grid-with-dots into a WK10 week-grid: 7 day columns w/ color-coded session chips (title + completed/scheduled), week nav + This-week jump, today highlighted, in the ClientPageLayout shell. Mobile = Runna-style day list. useClientWorkoutsWeek extended w/ title+date</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Calendar opened standalone (no left nav) + looked nothing like the WK10 design we built (was month dots). Hasan flagged both</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>pages/client/WorkoutCalendar.tsx (rewrite); hooks/useClientWorkouts.ts</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>TrueCoach week calendar; Runna day list</t>
+        </is>
+      </c>
+      <c r="J106" s="24" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (7608f0c) desktop + mobile; seeded a test program to confirm chips render</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -6001,7 +6001,7 @@
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Desktop: pair right-sized cards 2-col (Daily Targets + Log Today, Weekly Progress + Adherence, Coach + Care Team) instead of full-width stacking. Banners/hero stay full width; mobile stays stacked</t>
+          <t>Recompose dashboard into MAIN + RAIL: full-width Today hero on top; main column = nutrition target / this-week / adherence; rail = log today / coach (WhatsApp) / care team. Columns flow independently so short rail cards fill height vs a taller main -- no dead space. Replaces the forced equal-2col pairs</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="J102" s="24" t="inlineStr">
         <is>
-          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (fc77900): Targets+Log side by side confirmed live</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 desktop+mobile (609a9e9; earlier 2col fc77900). Balanced, important-first, grouped per Hasan geometry/flow note</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="J103" s="24" t="inlineStr">
         <is>
-          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (9937518): nutrition page now has left sidebar + flat bg</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (9937518 + bd66f70): ClientPageLayout shell wraps ClientNutrition, TeamNutrition, WorkoutCalendar, Messages, ExerciseHistory, AddonsCatalog. REMAINING: ClientSessions (4 returns) + shared multi-role Account/WorkoutLibrary/EducationalVideos (need role-aware layout)</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="J103" s="24" t="inlineStr">
         <is>
-          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (9937518 + bd66f70): ClientPageLayout shell wraps ClientNutrition, TeamNutrition, WorkoutCalendar, Messages, ExerciseHistory, AddonsCatalog. REMAINING: ClientSessions (4 returns) + shared multi-role Account/WorkoutLibrary/EducationalVideos (need role-aware layout)</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (9937518 + bd66f70): ClientPageLayout shell wraps ClientNutrition, TeamNutrition, WorkoutCalendar, Messages, ExerciseHistory, AddonsCatalog. REMAINING: ClientSessions (4 returns) + shared multi-role Account/WorkoutLibrary/EducationalVideos (need role-aware layout)  [UPDATE 2026-06-25: REMAINING done by CL10 -- ClientPageLayout now role-aware + wraps ClientSessions/Account/Learn.]</t>
         </is>
       </c>
     </row>
@@ -6240,6 +6240,214 @@
       <c r="J106" s="24" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (7608f0c) desktop + mobile; seeded a test program to confirm chips render</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NU10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Weekly check-in (ClientNutritionProgress)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Unify the whole weekly check-in into ONE guided surface: 3-level adherence scale (on_point/mostly/off_track + weighed/estimated/guessed) replacing yes/no; grouped Adherence + How-you-feel (changes + note) + cadence-gated Measurements (weight always; circumference odd weeks; body fat every 4th) with Steps folded in; dimmed dietitian-scoped Advanced seam. Persists note + physical_changes on adherence_logs.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Scattered adherence+changes across cards; richer signal; one phase-scoped write; extensible to dietitian questions.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nutrition/ClientNutritionProgress.tsx; nutrition/NutritionProgress.tsx; supabase/migrations 20260625120000 + 20260625130000; integrations/supabase/types.ts</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>visualize mock client_unified_checkin</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (a55d9b6 + 5f681a0 + 8144fb0): 3-level scale + derived compat booleans (lenient: mostly/estimated=true) so coach roster % math unchanged; steps fold-in; notes+physical_changes on adherence_logs. Caught + fixed pre-existing weekly_progress.goal_id FK landmine (nutrition_phases vs nutrition_goals disjoint) that 409d notes/body-fat for ALL phase clients -- check-in no longer writes weekly_progress; body fat relies on body_fat_logs. Supersedes NU9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CT5</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Library (Learn)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Merge Exercise Library + Educational Videos + Learning Paths into one /learn area: segmented Exercises . Videos . Pathways over a shared search; Exercises keeps full taxonomy facets; admin keeps video CMS in Videos tab; coach gets preview + assign. Old routes redirect; all nav repointed.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Three fragmented content surfaces; stop spreading features -- unify+simplify (Mobbin: NTC/MasterClass/Headspace single library + segmented tabs).</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>pages/Learn.tsx (new); components/learn/ExercisesTab.tsx + VideosTab.tsx (new); lib/routeConfig.ts; client/ClientSidebar.tsx; Navigation.tsx; client/QuickActionsGrid.tsx; App.tsx</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Nike Training Club / MasterClass / Headspace</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify. /workout-library -&gt; /learn?tab=exercises and /educational-videos -&gt; /learn?tab=videos redirect; sidebar/mobile-dock/top-nav/quick-action all repoint to Learn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>WK12</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Workout</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Workouts area (/client/workout/calendar)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Rename calendar -&gt; Workouts; Schedule/History in-page tabs (fold Exercise History in, remove its separate nav item); Week/Month toggle (default Month); month grid w/ status dots + legend + This-week enriched brief list (exercise count + primary muscles + Done/Due/Scheduled/Missed rails); enriched week chips; Message-coach button (-&gt; /messages); tap a month day to jump to that week.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Calendar was a bare week-grid; enrich + unify; month view is denser (Hasan pref); brief = exercise count + primary muscles.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>pages/client/WorkoutCalendar.tsx (rewrite); components/workouts/ExerciseHistoryPanel.tsx (new); hooks/useClientWorkouts.ts (enriched month/week selects + deriveModuleBrief); lib/routeConfig.ts; client/ClientSidebar.tsx; Navigation.tsx; App.tsx</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Runna / Nike Training Club</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify. Exercise History folded into Workouts&gt;History tab; /client/workout/history redirects to ?tab=history; nav item removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CL10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Role-aware ClientPageLayout + audit tail</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Make ClientPageLayout ROLE-AWARE (client -&gt; full sidebar shell; coach/admin -&gt; bare, top-nav only w/ correct role) via warm useRoleCache + fallback user_roles fetch. Wrap Learn, AccountManagement (2 branches), ClientSessions (4 branches) so staff stop getting the client sidebar / forced client role on shared multi-role routes.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Completes CL7: shared multi-role pages either lost the nav (bare) or would force the client shell on coaches/admins.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>components/layouts/ClientPageLayout.tsx; pages/Learn.tsx; pages/AccountManagement.tsx; pages/ClientSessions.tsx</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify incl. coach-login check on a shared page. Closes the CL7 REMAINING item (ClientSessions + role-aware shell for Account/Learn).</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -6343,7 +6343,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify. /workout-library -&gt; /learn?tab=exercises and /educational-videos -&gt; /learn?tab=videos redirect; sidebar/mobile-dock/top-nav/quick-action all repoint to Learn.</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (57321da) desktop+mobile: segmented Exercises/Videos/Pathways + shared search + full taxonomy facets; /workout-library and /educational-videos redirect into /learn; mobile dock shows Learn. Admin video-CMS + coach assign branches preserved.</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify. Exercise History folded into Workouts&gt;History tab; /client/workout/history redirects to ?tab=history; nav item removed.</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (57321da) desktop+mobile: Schedule/History tabs, Month default w/ status dots+legend + This-week briefs (status rails/pills), Week toggle enriched chips (count + status), folded ExerciseHistory panel, Message-coach, /client/workout/history redirect, dock renamed Workouts. (Seeded test program has 0 module_exercises so briefs show 0 exercises/no muscles -- count logic correct; real programs populate muscles.)</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>BUILT 2026-06-25, tsc-clean; PENDING push + live-verify incl. coach-login check on a shared page. Closes the CL7 REMAINING item (ClientSessions + role-aware shell for Account/Learn).</t>
+          <t>SHIPPED + LIVE-VERIFIED (client side) 2026-06-25 (57321da): client gets the sidebar shell on Learn/Workouts/Account; Account shows only the Account tab (no Coach Profile) for a client. PENDING: coach-login pass to confirm staff get the BARE shell (no client sidebar) on a shared route.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6448,6 +6448,162 @@
       <c r="J110" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED (client side) 2026-06-25 (57321da): client gets the sidebar shell on Learn/Workouts/Account; Account shows only the Account tab (no Coach Profile) for a client. PENDING: coach-login pass to confirm staff get the BARE shell (no client sidebar) on a shared route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CT6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Coach Hub (/coach/hub)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>New coach-only education area: segmented Training / Library / Resources over shared search. Library = advanced coach-only videos (category+level filters); Resources = ebooks/links + courses/certifications (redirect out). Generalized coach_educational_content (content_type/section/category/level/external_url/author); admin CMS extended; training gate scoped to section=training.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Centralizes advanced coaching education separate from client content; closes an RLS leak where any authenticated user could read coach content.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>src/pages/coach/CoachHub.tsx; CoachTrainingDashboard.tsx; admin/CoachEducationalContentManager.tsx; routeConfig.ts; App.tsx; migration 20260625140000</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>MasterClass; Crypto.com University</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-06-25 (c7dc303); coach live-verify pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CO10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>My Clients workspace (desktop)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Collapse the master client list to a 48px rail when a client is open so the detail pane gets the full canvas; chevron+clients-icon+attention-dot to expand into the full picker; auto-collapse on select. Desktop only; mobile keeps the drawer.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Coaches need room to read an individual client’s cards on desktop; the 220px master ate width with no payoff once focused.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>src/components/coach/CoachClientsWorkspace.tsx</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Linear; Height (master-detail collapse)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-06-25 (2863664); coach live-verify pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CO11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Coach shell + cards (design-language polish)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Flatten 3 leftover to-primary/5 gradients to bg-background (CoachDashboardLayout, CoachContentAssignments, TeamMemberNutritionDialog); swap macrocycle block &lt;Card onClick&gt; to ClickableCard (keyboard + aria-label).</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Brings coach surfaces in line with the flat-dark design language and a11y card pattern used everywhere else.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>src/components/coach/CoachDashboardLayout.tsx; CoachContentAssignments.tsx; TeamMemberNutritionDialog.tsx; programs/macrocycles/MacrocycleEditor.tsx</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-06-25 (2863664)</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6604,6 +6604,58 @@
       <c r="J113" t="inlineStr">
         <is>
           <t>SHIPPED 2026-06-25 (2863664)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CO12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Individual client overview (/coach/clients/:id)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Retire the redundant Progress tab (its CoachNutritionGraphs already lives in Nutrition-&gt;History; its VolumeChart already lives in Workouts). 8 sections -&gt; 7. Promote a compact phase-scoped weight-trend card onto Nutrition-&gt;Overview so the line is visible without drilling into History. Deep links to ?tab=progress degrade to default via the existing unknown-slug guard.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Removes a duplicate page; surfaces the weight trend one fewer click away. Simplify + avoid redundant pages.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>src/components/client-overview/sections.ts; ClientOverviewTabs.tsx; ClientOverviewNav.tsx; tabs/NutritionTab.tsx; nutrition/PhaseWeightTrendCard.tsx (new); tabs/ProgressTab.tsx (deleted)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Linear; Notion (consolidated detail views)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-06-25 (39050a3); coach live-verify pending</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6656,6 +6656,58 @@
       <c r="J114" t="inlineStr">
         <is>
           <t>SHIPPED 2026-06-25 (39050a3); coach live-verify pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CO13</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Coach</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Coach surfaces (polish pass)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Live-review polish: (1) weight-trend Y-domain now spans start+target so the target line is never off-chart; (2) new CoachShell wraps Coach Hub + Content Assignments so the left sidebar rail persists on those standalone pages; (3) Content Assignments empty-state copy points to Learn (was dead /educational-videos); program with no title falls back to macrocycle name then "Training program" (was "Untitled program"); (4) MetricCard hero value now font-mono+tabular app-wide; team cards equal-height + ClickableCard (was &lt;Card onClick&gt;). Capacity bars left as-is (load-encoded colours are intentional).</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Consistency + discoverability across the coach experience; removes dead copy and a11y/card anti-patterns.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>PhaseWeightTrendCard.tsx; useClientWorkouts.ts; coach/CoachShell.tsx (new); coach/teams/TeamCard.tsx; ui/metric-card.tsx; pages/coach/CoachHub.tsx; pages/coach/CoachContentAssignments.tsx</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Linear; Height</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (162155f)</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6708,6 +6708,58 @@
       <c r="J115" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-06-25 (162155f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DS1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Design foundation (typography + card primitive)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>App-wide foundation pass to close the gap between mockups and the live UI: (1) swap body typeface DM Sans -&gt; Geist (index.html link + tailwind sans token); (2) flatten the Card primitive -- drop shadow-sm so cards sit flat with a hairline border instead of the stock shadcn float; (3) cap font-bold at 600 via tailwind fontWeight theme override (every 700 header -&gt; crisp 600 in one place); (4) CardTitle 600 -&gt; 500. Bebas Neue display headlines + JetBrains Mono numerals unchanged.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Mockups read more premium than the site due to heavy 700 weights + shadowed stock-shadcn cards + generic font. Foundation-level fix lifts every page (client/coach/public/admin) at once.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>index.html; tailwind.config.ts; src/components/ui/card.tsx</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Linear; Vercel/Geist; Anthropic design system</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-26 (coach dashboard + client overview + public /services)</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J16" s="28" t="inlineStr">
         <is>
-          <t>Spec ready — small token pass on CoachOverviewStats / activity icons / compensation badges; no fabricated deltas. P2.</t>
+          <t>SHIPPED + LIVE-VERIFIED 2026-06-26 — metric cards carry interpretation/direction lines (e.g. "1 check-in due — 1 is 11d overdue", "7 of 7 clients active"); token pass folded into DS1 (mono numbers, flat cards). No fabricated deltas.</t>
         </is>
       </c>
     </row>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="J94" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/PR-Progress-Tab-Redesign-Spec.md</t>
+          <t>CLOSED 2026-06-26 — SUPERSEDED by CO12: the Progress tab was removed entirely (its CoachNutritionGraphs already lived in Nutrition-&gt;History; VolumeChart in Workouts) and a compact weight trend was promoted onto Nutrition-&gt;Overview. Redesign moot.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>CT1</t>
+          <t>CARE1</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="J95" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/CT-CareTeam-Tab-Redesign-Spec.md</t>
+          <t>Spec + mock ready - docs/CT-CareTeam-Tab-Redesign-Spec.md [ID renamed CT1-&gt;CARE1 2026-06-26 to resolve collision with CT1 Content/Library row 53.]</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>CL3</t>
+          <t>CL11</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="J97" s="24" t="inlineStr">
         <is>
-          <t>Increment 1 SHIPPED (commit a9b7fa6): flat surfaces (drop gradients) + macro ribbon on daily targets. Remaining: optional glance row + status-pill pass. Spec docs/CL2-Client-Dashboard-Polish-Spec.md</t>
+          <t>Increment 1 SHIPPED (commit a9b7fa6): flat surfaces (drop gradients) + macro ribbon on daily targets. Remaining: optional glance row + status-pill pass. Spec docs/CL2-Client-Dashboard-Polish-Spec.md [ID renamed CL3-&gt;CL11 2026-06-26 to resolve collision with CL3 LogTodayCard row 12.]</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>Shipped — merged main PR #167 (1b5f9c6), deploys to prod via Vercel. ExerciseHistory leads with Estimated-1RM trend MetricCard (Epley via shared helper; sparkline+delta+interpretE1rmTrend gated &gt;=2 sessions) + 3 per-session PR tiles; chronological table kept. Visual confirm at post-deploy smoke.</t>
+          <t>Shipped — merged main PR #167 (1b5f9c6), deploys to prod via Vercel. ExerciseHistory leads with Estimated-1RM trend MetricCard (Epley via shared helper; sparkline+delta+interpretE1rmTrend gated &gt;=2 sessions) + 3 per-session PR tiles; chronological table kept. Visual confirm at post-deploy smoke. || SUPERSEDED IN PART 2026-07-04: Hasan decision = NO e1RM anywhere in the app. Replace the Estimated-1RM trend card with ACTUAL logged rep-maxes (best load per rep count); true 1RM = coach programs a test day. Pending re-slice (small).</t>
         </is>
       </c>
     </row>
@@ -6760,6 +6760,102 @@
       <c r="J116" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-06-26 (coach dashboard + client overview + public /services)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>WK13</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Workout</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Program board + coach calendar</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Move session to another day: board kebab 'Move to day' (dated start-anchored picker) + 'apply to following weeks?' cascade prompt + coach-calendar move via move_plan_session RPC (1:1 clones only; team-shared rejected -&gt; 'edit from the team board')</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Coaches adjust a client schedule without rebuilding weeks; the one net-new board affordance from the redesign (B4/B5 tails)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>MuscleBuilderPage/SessionBlock/MobileDayDetail/ClientScheduleCalendar + move_plan_session RPC</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-07-02 (spec docs/DAY_MOVE_SLICE_BUILD.md). 3 smoke-found anchor-label bugs fixed same day (picker off-by-one, toast copy, mobile day-strip) - LESSON: all board weekday labels derive from assignment-start anchor, never Mon-first. Follow-up (merged 7ee0f02): copy/paste-day + remove-muscle toasts anchored too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>MS4</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Messaging</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Contextual comments</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Per-object comment threads on a logged session / weekly check-in / nutrition adjustment (coach&lt;-&gt;client two-way), distinct from general chat and care-team messages</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Feedback lives where it's relevant ('great pressing' on THE session); closes the redesign doc's B6 - last increment of COACH_CLIENT_REDESIGN.md</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>contextual_comments table + trigger + ContextualCommentThread; mounts: SessionLogViewer/NutritionCheckInCard/NutritionAdjustmentWeekCard/ClientNutritionProgress</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-07-03/04 (spec docs/B6_CONTEXTUAL_COMMENTS_BUILD.md; migration 20260703120000). RLS matrix + ownership trigger DB-proven; two-way check-in thread live; author names via get_coach_for_client (NOT coaches_client_safe - RLS-broken for clients). REMAINING fast-follows: client-side session+adjustment threads (no host surface yet), unread badges/notifications.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1163,6 +1163,11 @@
           <t>Ladder Coach chat</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-05 (commit 2ea3c17). formatUnreadBadge extracted to src/lib/unread.ts (shared w/ ClientSidebar); MobileBottomNav gains optional badge (visible-item pill + More-button dot + overflow-item badge, all guarded=additive); App.tsx MobileBottomNavClient injects useUnreadMessageCount(user.id) onto the /messages item. Verified as +online mobile viewport with a seeded unread: More-button red dot + overflow Messages "1" badge matching the RPC count; cleared to no-dot/no-badge on cleanup (count 0). Coach/admin docks unchanged (no messages destination). NOTE: deploy briefly served intermediate bundles (CDN mid-deploy) before stabilizing on index-5d0cjs_P -- hard-reload before trusting.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -1210,6 +1215,11 @@
           <t>Hevy / Future / Oura tab bars</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-05 (commit b5c4592, bundle index-DHL8mwnp). Client dock = 5 fixed tabs (Home/Nutrition/Workouts/Learn/Messages), no More overflow; Messages tab shows the CC3 unread badge on its icon (aria-label N unread). Verified +online mobile 375px + 320px (iPhone SE) -- 5 tabs flex evenly, no cramping, labels readable. Coach/admin docks unchanged (slice to &lt;=4, tight path never triggers). maxVisible=5 on client dock + tight=len&gt;=5 flex-1 min-w-0 + badge re-anchored to icon wrapper. CDN served prior bundle (DHCwaafi) on first check, propagated on retry.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -1306,7 +1316,12 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>Hevy / Fitbod skeletons</t>
+          <t>Fitbod/Hevy layout-shaped skeletons (sheet orig)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PARTIAL-&gt;WORSE (CC 2026-07-12): coach-side 53 files Loader2/spinner vs 4 Skeleton; client-side 9. Coach surface spinner-only. Full-page: CoachDashboardOverview:271, DietitianDashboardOverview:257, CoachMyClientsPage:1038, CoachSessions:408, ClientOverviewPanel:209. BUNDLE w/ CC10 error-sweep -&gt; one pass = skeleton + error branch per surface. // (prior) KEEP 2026-07-12 (still P1) -- shape skeletons to real components (MetricCard grids/roster rows). SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -1356,6 +1371,11 @@
           <t>Oura / Future home</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): NewClientOverview.tsx one-hero (TodaysWorkoutHero) + ranked single-column stack + right rail; 2-col grids gone (PR #178).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -1400,7 +1420,12 @@
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
-          <t>Fitbod / Hevy empty states</t>
+          <t>Fitbod/Hevy empty states (orig)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec to current bar: EmptyState primitive is house style now; scope = coverage audit + tasteful mono-icon/illustration slot, flat aesthetic. Merge w/ RO5. See DESIGN_BACKLOG_RECONCILIATION_2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -1554,6 +1579,11 @@
           <t>MacroFactor Adding a weight data</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): LogTodayCard.tsx:188-213 inline weight+steps Input + inline Log buttons, no navigation.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -1601,6 +1631,11 @@
           <t>Fitbod holding screens</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): ClientDashboardLayout.tsx:217-270 holding states (needs_medical_review / pending_coach_approval / pending_payment) as focused single-action Alert UI.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -1645,7 +1680,12 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Oura; Ladder Rewards</t>
+          <t>timespent Arcs gentle week-dots (mobbin.com/screens/9cc7a829-7e52-4fba-a224-d18fba39c85e); Me+ (…/68f3faa7). NOT QUITTR flame-streak (anti-pattern)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec to current bar: mono counter, GENTLE framing (no streak-pressure, wellbeing). Overlaps AD2 -- consolidate. Ground in Oura/Ladder. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1841,7 @@
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>Largely done — ClientActivityFeed already an avatar+relative-time feed. Polish only: add check-in/message types + team_id scoping. P2.</t>
+          <t>Largely done — ClientActivityFeed already an avatar+relative-time feed. Polish only: add check-in/message types + team_id scoping. P2. // Reviewed 2026-07-12 CC pass: leave as largely-done.</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1888,12 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Oura Activity goal gauge</t>
+          <t>Oura Activity Goal arc gauge (mobbin.com/screens/c8eceb02-6db4-4cfd-9a46-e1ed8fa90e0a)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec EnhancedCapacityCard as MetricCard-family filled gauge (18/25) in current tokens. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -2002,6 +2047,11 @@
           <t>Intercom context panel</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SUPERSEDED (verified 2026-07-05 recon): client overview uses horizontal section TABS (ClientOverviewNav/RD1), not an accordion. Board item moot.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -2046,7 +2096,12 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Intercom Reports</t>
+          <t>IGU CC1 MetricCard (house standard); Intercom Reports (orig)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- now a MetricCard grid (CC1 house style) + date-range filter; consistent coach/admin analytics. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -2252,6 +2307,11 @@
           <t>Internal consistency</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): CoachMyClientsPage + DietitianMyClientsPage share the same Card/Badge/Button roster language.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -2296,7 +2356,12 @@
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>EmptyState primitive</t>
+          <t>EmptyState primitive + Fitbod/Hevy</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- merge w/ CC8; flat/mono empty state "No clients need attention -- nice". See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -2346,6 +2411,11 @@
           <t>Hevy Logging a workout</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Superseded — tap-to-complete checkmark + lock state live in WorkoutSessionV2 (verified 2026-07-04); only tap-target polish remains</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -2395,7 +2465,7 @@
       </c>
       <c r="J29" s="28" t="inlineStr">
         <is>
-          <t>Open (re-scoped P1/S) — gap confirmed real at d428bf2: RestTimer is still a setInterval countdown over `remaining` state with NO wall-clock anchor (no Date.now endsAt), so it drifts/freezes on phone-lock/background. Auto-start + sticky already exist. Fix = anchor to wall-clock end time. Spec: WK2-WK3-Workout-Logging-Spec.md.</t>
+          <t>SHIPPED (commit 7b6be79, "Workout logging A1"): RestTimer re-anchored to wall-clock end time (endAt=Date.now()+duration*1000; every 250ms tick recomputes remaining from Date.now(); force-resync on visibilitychange+focus; pause/resume re-anchors endAt; firedRef single-fire). Fixes phone-lock/background drift. Working tree clean on main. Board status was stale (d428bf2 baseline predated the fix).</t>
         </is>
       </c>
     </row>
@@ -2497,6 +2567,11 @@
           <t>Hevy set rows</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SHIPPED (commit 7b6be79, "Workout logging A1"): ghost placeholders inside the set inputs show previous performance -- Weight placeholder = prefillWeightKg ?? historySet.weight; Reps = historySet.reps; RIR/RPE = historySet value (WorkoutSessionV2.tsx ~849-938) + fixed-height "last X" captions below each. Board status was stale (partial pre-7b6be79).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -2544,6 +2619,11 @@
           <t>Hevy Editing set type</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- still valid, correctly specced. Ground in Hevy set-type chip at build.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
@@ -2591,6 +2671,11 @@
           <t>Internal</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- internal consistency, still valid.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -2640,7 +2725,7 @@
       </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>Shipped — merged main PR #167 (1b5f9c6), deploys to prod via Vercel. ExerciseHistory leads with Estimated-1RM trend MetricCard (Epley via shared helper; sparkline+delta+interpretE1rmTrend gated &gt;=2 sessions) + 3 per-session PR tiles; chronological table kept. Visual confirm at post-deploy smoke. || SUPERSEDED IN PART 2026-07-04: Hasan decision = NO e1RM anywhere in the app. Replace the Estimated-1RM trend card with ACTUAL logged rep-maxes (best load per rep count); true 1RM = coach programs a test day. Pending re-slice (small).</t>
+          <t>Re-slice SHIPPED + LIVE-VERIFIED 2026-07-05 (commit 93fb9e6): Estimated-1RM (Epley) replaced with actual logged rep-maxes -- "Best load @ N reps" trend + rep-bracket chips + rep-max breakdown; canonical-read migration (fixes the B1 FK-embed break on the client history surface); oneRepMax.ts deleted; interpretE1rmTrend-&gt;interpretRepMaxTrend. Original PR #167 e1RM card superseded. Spec docs/HX1_REPMAX_BUILD.md.</t>
         </is>
       </c>
     </row>
@@ -2690,6 +2775,11 @@
           <t>Hevy Workout detail</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): SessionLogViewer.tsx read-only session recap (exercises/sets/load/reps/RIR/RPE), reached via calendar tap-to-recap (B5).</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -2737,6 +2827,11 @@
           <t>Hevy / Oura Calendar</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Largely shipped — canonical calendar dots (Done/Due/Scheduled/Missed) + tap-to-recap via SessionLogViewer (B5, 2026-07-01); confirm PR-crown marker</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -2784,6 +2879,11 @@
           <t>Fitbod Exercises by muscle / equipment</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): learn/ExercisesTab.tsx category tabs + muscle/region/subdivision filters + search + exercise cards (exercise-library redesign).</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -2831,6 +2931,11 @@
           <t>Hevy Muscle / Body distribution</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 (upgrade spec at build) -- high value; reuse useMusclePlanVolume (already computes volume). Ground in Hevy muscle/body distribution.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
@@ -2930,6 +3035,11 @@
           <t>MacroFactor Expenditure</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>KEEP-BLOCKED 2026-07-12 -- reasoning holds; revisit after food logging. // BLOCKED (verified 2026-07-07): the valuable TDEE trend = REVERSE/real TDEE (calculateReverseTDEE = avg calories consumed +- weight-change*7700/days) which needs calories-consumed data = FOOD LOGGING (deferred/FOR_LATER). Only the formula TDEE (calculateTDEE = BMR*activity) is computable now = a smooth low-insight curve as weight drops. Revisit AFTER food logging ships. Not worth building the formula-only version.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -3029,6 +3139,11 @@
           <t>Oura Activity goal; MacroFactor</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-07 (commit 7b03ca7, bundle D2rUF72z). ClientWeeklyRibbon tiles now show an interpretation line under the dots bar, per count. Verified +online (0/3, 0/7, Due): Weigh-ins -&gt; "Log your first weigh-in", Step days -&gt; "Log steps to start", Check-in -&gt; "Takes about 2 min". done-state shows emerald Goal met/Full week/Done this week. No data-model change.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -3076,6 +3191,11 @@
           <t>Oura Trends / Reports</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-07 (commit 09e6ff8, bundle CTyyX0ok). ClientNutrition (/nutrition-client) trend area = 4-tile metric-card stack (Weight 82.9kg / Body fat 14.4% / Adherence 100% "On plan 1/1 weeks" / Steps 8500 ↓2400) each w/ value+delta+sparkline+interpretation; active tile primary-ringed; 4W/12W/All range kept. Tap-to-expand verified: clicking Body fat moved the ring + swapped the detail chart below (Weight Trend -&gt; Body Fat 14.4% ↓0.3% w/ line chart); one at a time. Weight/Body-fat charts match old toggle. New NutritionMetricStack + NutritionTrendChart components + step_logs fetch. Mobile 390px = 2-up tiles, reflows, no overflow, 5-tab dock intact. Left column (hero/ribbon/log-today) unchanged. Team surface = parallel follow-up (not built). [FOLLOW-UP FIX cf3ed84 SHIPPED+VERIFIED 2026-07-07: delta chips overflowed the narrow 4-up tiles -&gt; fixed in the shared MetricCard primitive (metric-card.tsx: value+delta row flex-wrap + min-w-0 + DeltaChip shrink-0); delta now wraps under the value in-bounds; wide consumers (HX1 etc.) unchanged. NOTE: this commit hit the Vercel missed-webhook gotcha -- needed an empty-commit re-trigger (4624048); see feedback_vercel_missed_webhook_diagnose.]</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -3120,7 +3240,12 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>WHOOP Sharing my daily overview</t>
+          <t>Beli recap share card (mobbin.com/screens/ac5b8c7f-dee7-478c-aad7-8c89728720b1); Spotify Wrapped (…/9cc6cdc9)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- PhaseSummaryReport -&gt; branded exportable share image, current bar (Bebas hero kcal/weight, crimson, flat, WeightChangeProof chip). Ground in WHOOP sharing. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -3170,6 +3295,11 @@
           <t>Ladder Pinned messages</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>SHIPPED + FULLY COWORK-VERIFIED ON PROD 2026-07-05 (commit 70e73d4, migration 20260706113740, bundle index-DqFeVtf_). DB security gate PROVEN (jwt-impersonation): client-&gt;42501 "Only staff can pin messages", coach(primary)-&gt;{pinned:true}, anon-&gt;42501. COACH UI (viewing +online): PINNED section + unpin control (staff-only); clicking unpin fired the RPC -&gt; pinned_at/pinned_by cleared in DB + section removed + message intact. CLIENT UI (+online /messages): PINNED section read-only, NO pin controls. Multiple-pins model; realtime carries the pin (client render confirmed). Seed message cleaned up (thread pristine). Pre-existing minor (NOT MS1): coach sender name shows "Someone" on the client side. CDN served CC4 bundle ~25s before MS1 propagated.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -3217,6 +3347,11 @@
           <t>Ladder Coach chat</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SHIPPED (CLIENT DOCK ONLY) 2026-07-12: badge live MobileBottomNav.tsx:15-16,90-97 + App.tsx:142-145. CC-corrected scope: coach+admin docks have NO Messages item (CoachSidebar.tsx:232-234, AdminSidebar.tsx:131-146) -&gt; nothing to badge. Coach on mobile has no dock unread signal. Split -&gt; new row MS5.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -3264,6 +3399,11 @@
           <t>Ladder Chat / Community / Sending a cheer</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- net-new (existing coach_client/care_team messaging dont cover team-client community). Retention, big effort. Still valid.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
@@ -3311,6 +3451,11 @@
           <t>Fitbod onboarding; MacroFactor Setting up a goal</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- remaining = Skip affordance on optional steps + light momentum polish. Small scope. // PARTIAL (verified 2026-07-05 recon): OnboardingForm has persistent StepIndicator + single-focus steps, but NO Skip on optional steps.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -3355,7 +3500,12 @@
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
-          <t>Future Choosing a coach</t>
+          <t>Future Pro — Recommended Coaches card (mobbin.com/screens/50e21fab-5c26-4e05-a830-f99c0d1c6212) + coach profile Specialties/About (…/20fd4906) + Certified/Located (…/fc7492bc)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>SHIPPED + MERGED + PROD-DEPLOYED 2026-07-12 (squash 2902a3c, PR #189, deploy dpl_3khKUfuXpviVnbKaygFzLR1f5qJc READY; +445/-46, 6 files). Onboarding coach dialog now shows Located/Certified/derived headline/specialty chips/socials + View-full-profile deep-link to /coaches/:slug + mobile Drawer &lt;768px. Migration 20260712145922 (grants unchanged, no anon). 5 regression tests. CARRY-FWD: intro_video_url + years_experience null for both coaches (content task, not code); human click-through still pending (WaitlistGuard blocks CC). Was UPGRADE.</t>
         </is>
       </c>
     </row>
@@ -3405,6 +3555,11 @@
           <t>MacroFactor Setting up a goal / Customizing program</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- verify current onboarding nutrition-goal capture at build; likely still valid.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -3449,7 +3604,12 @@
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
-          <t>Hevy / Future / Oura Settings</t>
+          <t>Instagram Settings sectioned list (mobbin.com/screens/83c9dde8-a66e-4860-bfd4-dfc1c070827d); TheFork (…/048e0d20)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec AccountManagement to sectioned list: mono section heads + leading icons + chevrons + ClickableCard. Ground in Hevy/Oura settings. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -3499,6 +3659,11 @@
           <t>Future Canceling a membership</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>BUILT (verified 2026-07-05 recon): SubscriptionManagement.tsx:280-360 current plan + next_billing_date + explicit Cancel + cancel-reason textarea (retention beat).</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
@@ -3543,7 +3708,12 @@
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
-          <t>Centr Explore / Filtering</t>
+          <t>pliability Find-a-Session filter chips + heart-save (mobbin.com/screens/4c77a6bb-454c-482d-9f50-0b664acf0f64); Alan (…/58c27044)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- remaining = by-coach/equipment chips + Saved/Favourites shelf. Still valid. // PARTIAL (verified 2026-07-05 recon): Learn has search + category filter, but no by-coach/equipment filter chips and no Saved/Favourites shelf. SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -3593,6 +3763,11 @@
           <t>Centr Program details / Workout details</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-07 (commit 0290a71). /client/program/detail: header (plan "Classic Series...Meso (Copy)" + Calendar back btn) + overview (Week 2 of 8 + 2 of 40 sessions done) + vertical week sections (Week 1..) of session cards (Strength/type/7 exercises/muscles/status pill Done|Missed + Review|Start) + muted Rest rows. Verified: Review on the Done session opened the canonical player at correct assignment=74349417&amp;session=32dfcd7c&amp;date=2026-06-30 (all 3 params). Entry = "View full program" button in WorkoutCalendar header (confirmed live). Status derivation (Done/Missed/Rest) correct. Dock stays visible (/client prefix covers it; not the hidden /session path) -- CC deviation from spec accepted. Not tested: empty-state (no-assignment) + mobile 2-up (low-risk). Optional phase-2 exercise-name expand not built.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
@@ -3640,6 +3815,11 @@
           <t>Centr Coached workout</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- verification task on SecureVideoPlayer (cast/fullscreen/audio); keep watermark/secure access.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="11" t="inlineStr">
@@ -3687,6 +3867,11 @@
           <t>Centr Article detail</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>UPGRADE (conditional) 2026-07-12 -- gated on expanding written content; if built apply current typographic bar (Geist body, mono section labels). See recon 2026-07-12.md</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
@@ -3734,6 +3919,11 @@
           <t>Apple Fitness Adding / Reordering cards</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- power-user polish, strong curated default first. Low priority.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
@@ -3781,6 +3971,11 @@
           <t>Apple Fitness Awards / Award detail</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- retention, positive/health-aligned. Consolidate scope w/ CL5 streak (avoid two overlapping engagement surfaces).</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -3828,6 +4023,11 @@
           <t>WHOOP / Oura Reports</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>PARTIAL (CC-corrected 2026-07-12): send-weekly-coach-digest is an ACTIVITY digest, not a PROGRESS one -- index.ts:97-117 counts exercise_set_logs&gt;0 per client and throws magnitude away; body = Total/Active/Inactive/New stat cards. No weight trend/adherence/volume/PRs/check-ins. AD3 roster-PROGRESS ask STILL OPEN. Cron confirmed (vercel.json:4).</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="11" t="inlineStr">
@@ -3875,6 +4075,11 @@
           <t>Future Scheduling a call with coach</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>KEEP 2026-07-12 -- overlaps Sessions booking (SE1); fold into that phase, not standalone. Depends on SE1 (locked: session_bookings model).</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -4127,7 +4332,12 @@
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
-          <t>Standard pattern</t>
+          <t>Standard pattern (flat bar)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec HowItWorksSection to flat surfaces, mono step labels, crimson accents. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4384,12 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>Standard pattern</t>
+          <t>Contractbook outcome-led testimonial grid (mobbin.com/sites/sections/e66be7ae-4850-4bf8-8327-64e641e1c6b3) + Shade case-study cards (…/ba35c5dc)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>UPGRADE + BIGGER BUG (CC 2026-07-12): (1) reorder card lead-with-outcome (order today stars:109-119&gt;quote&gt;proof:121-123&gt;author). (2) FABRICATED social proof -- TestimonialsList.tsx:142-162 renders 3 fake 5-star "Client Name/Program Type" cards when no featured testimonials (also the error fallback :87). PUB6 asked AUTHENTIC -&gt; killing the fakes is the bigger win. (3) no useTranslation on i18n public page. Spec: DESIGN_UPGRADE_PASS_2026-07-12.md</t>
         </is>
       </c>
     </row>
@@ -4224,6 +4439,11 @@
           <t>Standard pattern</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>KEEP + light UPGRADE 2026-07-12 -- content audit (price/commitment/refunds/medical) + flat accordion in current bar. See recon 2026-07-12.md</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="42" customHeight="1">
       <c r="A68" s="11" t="inlineStr">
@@ -4271,6 +4491,11 @@
           <t>Internal consistency</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SHIPPED + LIVE-VERIFIED 2026-07-04 (Cowork prod verify) -- strict app-parity flatten of public pages (removed gradients/raw rgba, tokenized) + BTN1 gradient-button retirement shipped alongside. Specs docs/PUB8_PUBLIC_PAGES_ALIGNMENT_BUILD.md + docs/BTN1_RETIRE_GRADIENT_BUTTONS_BUILD.md.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="42" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
@@ -4367,7 +4592,12 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>Standard pattern</t>
+          <t>Standard pattern (flat bar)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>UPGRADE 2026-07-12 -- re-spec Waitlist.tsx to current bar + explicit what-happens-next copy. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4649,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>KEEP 2026-07-12 -- token consistency (CC5). // Backlog</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4701,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>KEEP 2026-07-12 -- dedupe phase-status logic. // Backlog</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4753,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>KEEP 2026-07-12 -- needs upstream signed WoW first. // Backlog</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4785,7 @@
       </c>
       <c r="F74" s="26" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4575,7 +4805,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>P1/BUG (bumped 2026-07-12, Hasan): data-correctness bug -- WeeklyProgressCard "This Week" trend skewed by outlier/zero weigh-in (e.g. +17.5kg). Fix = smoothed weekly-avg trend (NU1-consistent) + exclude zero/invalid. client/WeeklyProgressCard.tsx.</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5325,7 @@
       </c>
       <c r="J84" s="24" t="inlineStr">
         <is>
-          <t>Reported - bugs cowork (likely test data)</t>
+          <t>Reported - bugs cowork (likely test data) // Reviewed 2026-07-12: likely test data, verify at build.</t>
         </is>
       </c>
     </row>
@@ -5454,12 +5684,12 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Calendly / Cal.com booking; Practo appointments</t>
+          <t>Zomato Your Bookings Upcoming/History+status pills (mobbin.com/screens/b2da1a7b-4031-4299-88e6-4942956cd1bc); Urban Company (…/d2b44cff); Redfin (…/3e51ab5e)</t>
         </is>
       </c>
       <c r="J91" s="24" t="inlineStr">
         <is>
-          <t>Spec ready - docs/SE-Sessions-Tab-Booking-Spec.md (CC handoff)</t>
+          <t>RE-SPEC FROM SCRATCH (CC 2026-07-12): spec targets the WRONG system. Client /sessions (ClientSessions.tsx:135,147,168) reads session_bookings+coach_time_slots+book_session_atomic, NOT direct_calendar_sessions (only 2 coach components read that). "both surfaces read d_c_s" false; "extend status CHECK" moot (no CHECK, free text 20260205:76); availability model ALREADY ships (coach_time_slots/CoachSessions.tsx). ARCH DECISION: build request-&gt;confirm on existing session_bookings [rec] vs unify d_c_s. Gates AD4+GC1+BUG13; orphans /coach/sessions. DECISION LOCKED 2026-07-12: build request-&gt;confirm on EXISTING session_bookings/coach_time_slots (not a parallel d_c_s system). Re-spec pending. SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5736,12 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>TrueCoach calendar; Runna day-list</t>
+          <t>Runna Training calendar per-day +Add (mobbin.com/screens/86245523-ea19-44cd-bb20-5b52f0bbaa88); Aaptiv Edit My Plan (…/d0021aaa)</t>
         </is>
       </c>
       <c r="J92" s="24" t="inlineStr">
         <is>
-          <t>Spec ready - docs/WK-Coach-Workouts-Calendar-Spec.md (CC handoff)</t>
+          <t>KEEP 2026-07-12 (upgrade spec) -- ground authoring +menu in TrueCoach/Runna at build. // PARTIAL (verified 2026-07-05 recon): B5 read-only week/month coach calendar (ClientScheduleCalendar) exists; the WK10 net-new piece = per-day +menu authoring (Blank/Saved/Assign program/Create) is OPEN. SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5793,7 @@
       </c>
       <c r="J93" s="24" t="inlineStr">
         <is>
-          <t>Future phase - after Sessions booking (Phase 2) ships. Captured; not started</t>
+          <t>KEEP 2026-07-12 (future) -- gated on Sessions booking Phase 2. Correctly parked. // Future phase - after Sessions booking (Phase 2) ships. Captured; not started</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5897,7 @@
       </c>
       <c r="J95" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/CT-CareTeam-Tab-Redesign-Spec.md [ID renamed CT1-&gt;CARE1 2026-06-26 to resolve collision with CT1 Content/Library row 53.]</t>
+          <t>DONE (verified 2026-07-12): role chips CareTeamCard.tsx:85-95,321 + staff-only banner :236-240 + own/other bubbles CareTeamMessagesPanel.tsx:403-467 all confirmed; only optional @-mentions absent -&gt; close (split a new low-pri row if wanted). // LARGELY SHIPPED (via specialist-parity S1-S5 + messaging work) -- verified 2026-07-05. CareTeamCard has header + Add Specialist (gated) + staff-only banner (Lock, line 237) + role-coloured chips (SPECIALTY_CONFIG) + Ends chip + You badge + kebab discharge/terminate. CareTeamMessagesPanel has threaded own/other bubbles (isOwn-&gt;flex-row-reverse + bg-primary vs bg-muted, line 404-438) + avatars + pinned composer. Spec substance done. REMAINING = cosmetic only (raw Tailwind chip colors bg-green-100 vs redesign token soft-pills; specialty ICON avatars vs initials; own-bubble bg-primary vs --color-background-info; @mention highlight unconfirmed) -- optional P2 polish, not a required slice.</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5949,7 @@
       </c>
       <c r="J96" s="24" t="inlineStr">
         <is>
-          <t>Spec + mock ready - docs/PF-Profile-Tab-Redesign-Spec.md</t>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-05 (commit 29e4a06, bundle index-DHCwaafi). ProfileInfoTab now leads with an identity header card (avatar initials + name + &lt;plan&gt; subtitle + soft status pill; client-since from submission.createdAt, omitted when null); subscription + onboarding shadcn Badges swapped to the redesign soft-tinted rounded-full pill (border-status-X/40 bg-status-X/10 text-status-X via a shared inline StatusPill, colors via getSubscriptionStatusVariant); demographics/onboarding grids -&gt; auto-fit minmax(8rem,1fr) reflow (CC deviated from spec minmax(0,1fr) which would 1-up-collapse). Verified live coach viewing +online: header + soft Active pill render, pills consistent w/ Overview/Nutrition, no console errors (stale HX1-bundle auth transients only). NOT exercised (data, not bugs): client-since populated + review-needed medical rail (no test client w/ a submission handy). NOTE: deploy served the prior bundle (5d0cjs_P) on first check, propagated to DHCwaafi on retry -- CDN timing, hard-reload before trusting.</t>
         </is>
       </c>
     </row>
@@ -6804,7 +7034,6 @@
           <t>MuscleBuilderPage/SessionBlock/MobileDayDetail/ClientScheduleCalendar + move_plan_session RPC</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-07-02 (spec docs/DAY_MOVE_SLICE_BUILD.md). 3 smoke-found anchor-label bugs fixed same day (picker off-by-one, toast copy, mobile day-strip) - LESSON: all board weekday labels derive from assignment-start anchor, never Mon-first. Follow-up (merged 7ee0f02): copy/paste-day + remove-muscle toasts anchored too.</t>
@@ -6852,10 +7081,519 @@
           <t>contextual_comments table + trigger + ContextualCommentThread; mounts: SessionLogViewer/NutritionCheckInCard/NutritionAdjustmentWeekCard/ClientNutritionProgress</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>SHIPPED + LIVE-VERIFIED 2026-07-03/04 (spec docs/B6_CONTEXTUAL_COMMENTS_BUILD.md; migration 20260703120000). RLS matrix + ownership trigger DB-proven; two-way check-in thread live; author names via get_coach_for_client (NOT coaches_client_safe - RLS-broken for clients). REMAINING fast-follows: client-side session+adjustment threads (no host surface yet), unread badges/notifications.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>UN1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cross-cutting / Identity</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Messaging + Account/Profile (cross-role)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Introduce a user-chosen username/handle as the cross-role DISPLAY identity. Show it as the sender name in coach&lt;-&gt;client messages and wherever a name renders across roles. Settable in account settings (and/or onboarding); unique + reserved-word handling; backfill/default for existing users; exposed via an RLS-safe client-readable path so both roles can resolve it.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Client message view shows the coach as "Someone" today -- sender names resolve only from profiles_public, which a client cannot read for a coach (coaches live in coaches/coaches_public). A username is a shareable, RLS-safe, stable identity that removes per-surface name-resolution hacks.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>src/components/messaging/CoachClientThread.tsx (sender resolve ~L138); profiles/coaches schema (new username col); account settings; get_coach_for_client (interim)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>SHIPPED + COWORK-VERIFIED ON PROD 2026-07-05 (commit 4a1a9dc, migration 20260706173434, bundle index-CAjo31y9). DB PROVEN via jwt-impersonation: cross-role fix = as the client, direct profiles_public read of the coach returns 0 rows (RLS) BUT get_public_identities returns the coach username "hasandashti3" -- the exact Someone gap closed. set_username rejects reserved ("That username is reserved") + case-insensitive taken ("taken") + valid succeeds {ok:true}; anon-&gt;42501 on the resolver. Backfill: 0 null / 0 case-insensitive dup / 0 reserved (coach=hasandashti3, +online=hdx1). UI account settings (/account): @ Username card renders -- helper "public handle, shown as your name in messages, letters/numbers/underscores 3-20", @-prefixed input w/ current handle, Save. MESSAGE-RENDER SMOKE PASSED 2026-07-05: seeded a coach msg, viewed as +online client -&gt; sender rendered the coach USERNAME ("DrIron", after Hasan changed it from backfill hasandashti3 via the account-settings field = SET path also confirmed), NOT "Someone", NOT display_name ("Hasan Dashti"). Full end-to-end pass. Phase 2 (noted, not built): care-team/coach-cards/onboarding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>BUG12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Navigation / bug</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Top navbar user Menu (desktop DropdownMenu)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Desktop nav user-menu wont open when the page is scrolled -- opening it appears to collapse; user must scroll to top to use it. Fix: set modal={false} on the DropdownMenu in Navigation.tsx (~L463).</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Root cause (Cowork-diagnosed live 2026-07-05): the Radix DropdownMenu is modal by default -&gt; on open it applies react-remove-scroll scroll-lock which mutates body/html overflow and BREAKS the sticky nav (position:sticky top:0). DOM-proven: menu open -&gt; nav.top=-600 (off-screen, scrollY 600) + body scroll-locked + the menu IS open but anchored off-screen; menu closed -&gt; nav.top=0 sticky OK. So the menu opens off-screen = looks collapsed.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>src/components/Navigation.tsx ~L463 (DropdownMenu -&gt; modal={false})</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>FIXED + COWORK-VERIFIED ON PROD 2026-07-05 (commit dc7ca65, bundle index-mKrveo4n). modal={false} on Navigation.tsx desktop DropdownMenu. DOM-proven: scrolled 1200px, open Menu -&gt; nav stays sticky top:0 (was -600), dropdown open + ON-SCREEN (top:56, anchored to trigger), no body scroll-lock; visually confirmed dropdown renders (Role/Dashboard links/Account/Sign Out); Escape closes cleanly, nav stays sticky. Bug (menu opening off-screen when scrolled) resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CC10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Add a visible error branch to every data surface; stop degrading fetch failures into empty/placeholder states. Bundle with CC6 (same ~53 files) -- one pass = layout-shaped skeleton + error branch per surface.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SYSTEMIC: 0 of 16 audited shipped surfaces have a visible error branch. Actively misleading -- CoachAlerts.tsx:96 shows "0 alerts" on fetch fail; MeetOurTeam:76 shows "team being assembled" on a blip; TestimonialsList:87 falls back to 3 FAKE 5-star cards; CoachPublicPage:98 collapses errors+404. Contradicts CLAUDE.md {error} destructure-and-throw (Client Overview tabs swallow it: NutritionTab:86, CareTeamTab:115, SessionsTab:111, OverviewTab:119, ProfileInfoTab:100).</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>coach/CoachAlerts.tsx:96, pages/MeetOurTeam.tsx:76, marketing/TestimonialsList.tsx:87, pages/CoachPublicPage.tsx:98, client-overview/tabs/*</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12). Highest new-item priority; sequence above CT1. Cheap: error var + branch per surface. SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CC9</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>A11y / ClickableCard</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Replace 13 &lt;Card onClick&gt; with &lt;ClickableCard&gt; (role=button/tabIndex/Enter-Space/focus ring). Also AlertsCard.tsx:70 onClick on &lt;Alert&gt;.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>CLAUDE.md mandates ClickableCard; 13 sites bypass it -&gt; keyboard-inaccessible nav/action cards.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>client/QuickActionsGrid.tsx:50, coach/CoachAlerts.tsx:113/129/145, admin/AdminMetricsCards.tsx:205, admin/AdminBillingManager.tsx:554, admin/SiteContentManager.tsx:166, client/ClientDashboardLayout.tsx:736, coach/CoachClientDetail.tsx:497, coach/programs/ProgramEditor.tsx:431, coach/programs/macrocycles/MacrocycleEditor.tsx:549, pages/ClientSubmission.tsx:222, pages/coach/CoachTrainingDashboard.tsx:289/328, client/AlertsCard.tsx:70</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ui/clickable-card.tsx pattern</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DS2</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Flat surfaces</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Extend PUB8 flatten to authed shells: remove bg-gradient-to-br page washes (admin/client/auth), retire surviving gradient button (PaymentStatusDashboard:732), replace gradient-clipped hero numbers (CalorieResults:47/90, AdjustmentCalculator:641) with flat Bebas crimson, drop from-primary-to-accent icon medallions.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PUB8/BTN1 flattened public pages; admin/client/auth shells never got the pass -&gt; pre-flatten gradient signature persists on authed surfaces. Gradient-clipped hero numbers directly contradict the Bebas-flat-crimson bar.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>admin/AdminPageLayout.tsx:87, admin/AdminDashboardLayout.tsx:151, pages/WorkoutLibrary.tsx, pages/EducationalVideos.tsx, pages/BillingPayment.tsx, pages/PaymentStatus.tsx, pages/PaymentReturn.tsx, Auth/ResetPassword/EmailPending/EmailConfirmed/NotFound/Unauthorized/CoachSignup/CoachPasswordSetup, calculator/CalorieResults.tsx, calculator/AdjustmentCalculator.tsx, PaymentStatusDashboard.tsx:732</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>PUB8 flatten precedent</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DS3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Shadow discipline</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Remove caller-added shadows (46 sites outside ui/). RULING LOCKED 2026-07-12: CHANGE THE PRIMITIVE -- swap clickable-card.tsx:52 hover:shadow-md for a border/bg hover so ClickableCard obeys the flat bar (fixes ~26 call sites at source).</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Card primitive is correctly flat (ui/card.tsx:6) but callers re-add shadow-lg/md, and the sanctioned ClickableCard violates the no-shadow bar at source.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>ui/clickable-card.tsx:52, PaymentStatusDashboard.tsx:463/477/502, coach/CoachAlerts.tsx:114/130/146, client/QuickActionsGrid.tsx:52, admin/AdminMetricsCards.tsx:207, ProgramLibrary.tsx:565, +~35 more (CC scan)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>OPEN (ruling locked: change primitive) (new, CC 2026-07-12). See design-owner decision doc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CC11</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>i18n / RTL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>i18n + RTL pass on shipped/public surfaces: add useTranslation where missing; swap physical mr-/ml-/left-/pl- for logical me-/ms-/start/ps- so Arabic dir-flip works.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>App is en/ar with dir flip. Public surfaces have hardcoded English (MeetOurTeam ~9 strings, Testimonials, TestimonialsList no useTranslation) + physical-direction classes (search icons wrong side in Arabic: TestimonialsManager:283, CoachMyClientsPage:1003; NutritionPhaseCard:184/225/231). CoachPublicProfile headline flows untranslated into the SEOHead title.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>pages/MeetOurTeam.tsx, pages/Testimonials.tsx, marketing/TestimonialsList.tsx, nutrition/NutritionPhaseCard.tsx:184/225/231, coach/CoachSessions.tsx, client-overview/tabs/NutritionTab.tsx:243/326, coach/CoachPublicProfile.tsx:61</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>MS5</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Messaging</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Mobile dock</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Give coach + admin mobile docks a Messages item with an unread badge (client dock already has it). Reuse useStaffUnreadCounts / get_unread_message_counts_for_staff (already consumed in CoachMyClientsPage).</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>MS2 shipped on the client dock only; coach/admin docks have no Messages item -&gt; a coach/admin on mobile has no dock-level unread signal.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>App.tsx:154-224, coach/CoachSidebar.tsx:232, admin/AdminSidebar.tsx:131, hooks/useStaffUnreadCounts</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>OPEN (new, split from MS2, CC 2026-07-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PUB11</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Public / Marketing</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Coach page SEO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Add Schema.org AggregateRating/Review JSON-LD to CoachPublicPage (deferred in T2 to T1; T1 never built it -- zero ld+json in src today).</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Orphaned deferral + real SEO miss on a page whose whole point is reputation; the rating aggregate is already fetched (CoachPublicPage:90-91,201-203), just not marked up.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>pages/CoachPublicPage.tsx, components/SEOHead.tsx</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BUG13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Client visibility</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Coach-created direct_calendar_sessions never render on the client side (client /sessions reads session_bookings only). Surface them to clients, or fold direct sessions into the booking model (see SE1 decision).</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RLS permits client SELECT on direct_calendar_sessions but no client code reads it (only SessionsTab.tsx:82 + DirectClientCalendar.tsx:93, both coach). Coach schedules a session; the client never sees it. Live bug, not a design nicety.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>pages/ClientSessions.tsx, client-overview/tabs/SessionsTab.tsx:82, coach/programs/DirectClientCalendar.tsx:93</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>OPEN (new, CC 2026-07-12). Tied to the SE1 architecture decision. SE1 model locked to session_bookings -&gt; surfacing coach direct sessions likely folds into that unification.</t>
         </is>
       </c>
     </row>

--- a/docs/IGU-Design-Changes-Master.xlsx
+++ b/docs/IGU-Design-Changes-Master.xlsx
@@ -1321,7 +1321,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PARTIAL-&gt;WORSE (CC 2026-07-12): coach-side 53 files Loader2/spinner vs 4 Skeleton; client-side 9. Coach surface spinner-only. Full-page: CoachDashboardOverview:271, DietitianDashboardOverview:257, CoachMyClientsPage:1038, CoachSessions:408, ClientOverviewPanel:209. BUNDLE w/ CC10 error-sweep -&gt; one pass = skeleton + error branch per surface. // (prior) KEEP 2026-07-12 (still P1) -- shape skeletons to real components (MetricCard grids/roster rows). SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+          <t>PARTIAL-&gt;BUILT-CORE 2026-07-12 (feat/cc6-cc10-...): skeleton shells (MetricCardGrid/RosterRow/TabShell) + 15 priority surfaces done bundled w/ CC10. CC6-TAIL = remaining ~40 coach Loader2-&gt;skeleton conversions DEFERRED (low-value polish, follow-up PR if wanted). // PARTIAL-&gt;WORSE (CC 2026-07-12): coach-side 53 files Loader2/spinner vs 4 Skeleton; client-side 9. Coach surface spinner-only. Full-page: CoachDashboardOverview:271, DietitianDashboardOverview:257, CoachMyClientsPage:1038, CoachSessions:408, ClientOverviewPanel:209. BUNDLE w/ CC10 error-sweep -&gt; one pass = skeleton + error branch per surface. // (prior) KEEP 2026-07-12 (still P1) -- shape skeletons to real components (MetricCard grids/roster rows). SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>UPGRADE 2026-07-12 -- re-spec to current bar: mono counter, GENTLE framing (no streak-pressure, wellbeing). Overlaps AD2 -- consolidate. Ground in Oura/Ladder. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+          <t>BUILT 2026-07-12 (branch feat/cl5-weekly-consistency, off main, PR pending): WeekConsistencyDots near TodaysWorkoutHero in NewClientOverview -- Mon-Sun dots (filled crimson=active day, outline=not) + "N active days this week". Active=workout logged that day (exercise_set_logs, Kuwait wall-clock buckets, IGU Monday week). useWeeklyConsistency hook (read) + presentational dots. GENTLE enforced by tests: no red/warning at any level, no streak/missed/chain/flame/failed copy, zero-week says just "0 active days" no nudge, AND no fanfare on full week (celebration = same pressure lever). Skipped sets excluded; failed read omits row (CC10 lesson). 349/349 tests (+9), tsc 301. Was UPGRADE.</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UPGRADE 2026-07-12 -- re-spec EnhancedCapacityCard as MetricCard-family filled gauge (18/25) in current tokens. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+          <t>BUILT 2026-07-12 (branch feat/co4-capacity-gauge, off main, PR pending): EnhancedCapacityCard 3 text stats -&gt; Oura-style semicircle arc gauge, Bebas hero count, mono "18/25 · 72% CAPACITY" + CC2 plain-language read. Crimson-&gt;amber(--status-warning) at &gt;=90%, NO green/red (neutral load, test-enforced across 0/72/100/120%). Over-cap clamps fill to 1; no-cap omits arc. Also neutralized 2 adjacent badges (spots-left green-&gt;muted, over-by destructive-&gt;amber) for coherence. getLoadColor per-service rows LEFT for FU1 (commented). 335/335 tests (+9), tsc 301. Was UPGRADE.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>UPGRADE 2026-07-12 -- re-spec AccountManagement to sectioned list: mono section heads + leading icons + chevrons + ClickableCard. Ground in Hevy/Oura settings. See recon 2026-07-12.md SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+          <t>DOWNGRADED to minor polish 2026-07-12 (stale premise): AccountManagement.tsx:1118L is ALREADY sectioned (Profile/Security/Coaching &amp; Billing/Account Safety, uppercase tracking-wide heads) AND form-heavy (username save / coach-change / cancel / delete) -- NOT a flat nav list. The "flat-&gt;grouped chevron rows" rec would fight the inline forms. Real delta = small cosmetic: mono + primary-tick section heads, leading icons, flat cards, ClickableCard for genuine nav rows only. Effort S-&gt;XS. Lower value than net-new CL5/NU6.</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>KEEP 2026-07-12 -- retention, positive/health-aligned. Consolidate scope w/ CL5 streak (avoid two overlapping engagement surfaces).</t>
+          <t>SUPERSEDED by CL5 2026-07-12 -- no separate awards/trophy surface (noted in WeekConsistencyDots component so nobody adds one); any milestones ride as gentle callouts on the consistency row, not a gamified wall. KEEP 2026-07-12 -- retention, positive/health-aligned. Consolidate scope w/ CL5 streak (avoid two overlapping engagement surfaces).</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>UPGRADE + BIGGER BUG (CC 2026-07-12): (1) reorder card lead-with-outcome (order today stars:109-119&gt;quote&gt;proof:121-123&gt;author). (2) FABRICATED social proof -- TestimonialsList.tsx:142-162 renders 3 fake 5-star "Client Name/Program Type" cards when no featured testimonials (also the error fallback :87). PUB6 asked AUTHENTIC -&gt; killing the fakes is the bigger win. (3) no useTranslation on i18n public page. Spec: DESIGN_UPGRADE_PASS_2026-07-12.md</t>
+          <t>BUILT 2026-07-12 (branch feat/pub6-testimonials-outcome-led, on top of #195, PR pending): (1) fabricated 3-fake-card empty state KILLED -&gt; real EmptyState; (2) card reordered result-hero-&gt;quote-&gt;author-&gt;small stars footer, attachment-less cards stay quote-led; (3) i18n added (5 keys, en/ar parity 89/89), hardcoded "Coach:" removed. Neutral hero enforced by test (no crimson/success class). 331/331 tests (+5), tsc 301 (0 new). CC10 error branch untouched. Was UPGRADE.</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>KEEP 2026-07-12 -- token consistency (CC5). // Backlog</t>
+          <t>KEEP 2026-07-12 -- token consistency (CC5). // Backlog // More relevant post-CO4: the per-service-row getLoadColor (green/amber/red) now visibly clashes with CO4 neutral gauge — CO4 flagged it in-comment. Consider bumping.</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>OPEN (new, CC 2026-07-12). Highest new-item priority; sequence above CT1. Cheap: error var + branch per surface. SPEC: DESIGN_UPGRADE_SPECS_BATCH2_2026-07-12.md.</t>
+          <t>BUILT 2026-07-12 (branch feat/cc6-cc10-skeletons-error-states, PR pending): shared LoadError + skeleton shells; 15 surfaces swept; 4 liars (CoachAlerts/MeetOurTeam/TestimonialsList error branch/CoachPublicPage) now LoadError w/ 2-directional regression tests. Tests forced out 2 real bugs: CoachAlerts never threw (dead error branch, CLAUDE.md {error} violation) + CoachPublicPage error-vs-!data conflation. tsc 301 (0 new), 326/326 tests. TestimonialsList empty-state fakes + card order LEFT for PUB6.</t>
         </is>
       </c>
     </row>
